--- a/SpaceDebris_site_1000/2007-020IA_Blok-I_Soyuz-FG_Fregat.xlsx
+++ b/SpaceDebris_site_1000/2007-020IA_Blok-I_Soyuz-FG_Fregat.xlsx
@@ -452,7002 +452,7002 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>159.36</v>
+        <v>0.08</v>
       </c>
       <c r="B2" t="n">
-        <v>23938</v>
+        <v>37549</v>
       </c>
       <c r="C2" t="n">
-        <v>152.76</v>
+        <v>2.24</v>
       </c>
       <c r="D2" t="n">
-        <v>14085</v>
+        <v>22763</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>175.97</v>
+        <v>0.29</v>
       </c>
       <c r="B3" t="n">
-        <v>21250</v>
+        <v>38356</v>
       </c>
       <c r="C3" t="n">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>28801</v>
+        <v>17886</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95.59</v>
+        <v>0.44</v>
       </c>
       <c r="B4" t="n">
-        <v>36383</v>
+        <v>36939</v>
       </c>
       <c r="C4" t="n">
-        <v>94.70999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="D4" t="n">
-        <v>14712</v>
+        <v>21883</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91.69</v>
+        <v>0.53</v>
       </c>
       <c r="B5" t="n">
-        <v>26503</v>
+        <v>36169</v>
       </c>
       <c r="C5" t="n">
-        <v>93.89</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>22514</v>
+        <v>21603</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94.59</v>
+        <v>0.74</v>
       </c>
       <c r="B6" t="n">
-        <v>32939</v>
+        <v>35748</v>
       </c>
       <c r="C6" t="n">
-        <v>93.58</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>29612</v>
+        <v>27684</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>34.78</v>
+        <v>1.71</v>
       </c>
       <c r="B7" t="n">
-        <v>24264</v>
+        <v>37677</v>
       </c>
       <c r="C7" t="n">
-        <v>33.71</v>
+        <v>8.02</v>
       </c>
       <c r="D7" t="n">
-        <v>27412</v>
+        <v>29311</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97.34999999999999</v>
+        <v>2.33</v>
       </c>
       <c r="B8" t="n">
-        <v>40890</v>
+        <v>38467</v>
       </c>
       <c r="C8" t="n">
-        <v>97.27</v>
+        <v>10.97</v>
       </c>
       <c r="D8" t="n">
-        <v>23618</v>
+        <v>17019</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>160.18</v>
+        <v>2.34</v>
       </c>
       <c r="B9" t="n">
-        <v>21787</v>
+        <v>37751</v>
       </c>
       <c r="C9" t="n">
-        <v>154.69</v>
+        <v>1.79</v>
       </c>
       <c r="D9" t="n">
-        <v>11751</v>
+        <v>27092</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>42.19</v>
+        <v>2.75</v>
       </c>
       <c r="B10" t="n">
-        <v>23452</v>
+        <v>36433</v>
       </c>
       <c r="C10" t="n">
-        <v>43.37</v>
+        <v>5.02</v>
       </c>
       <c r="D10" t="n">
-        <v>23275</v>
+        <v>26749</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99.63</v>
+        <v>3.08</v>
       </c>
       <c r="B11" t="n">
-        <v>43007</v>
+        <v>36253</v>
       </c>
       <c r="C11" t="n">
-        <v>103.7</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>16754</v>
+        <v>28381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>91.48999999999999</v>
+        <v>3.31</v>
       </c>
       <c r="B12" t="n">
-        <v>24864</v>
+        <v>35831</v>
       </c>
       <c r="C12" t="n">
-        <v>89.47</v>
+        <v>0.95</v>
       </c>
       <c r="D12" t="n">
-        <v>13538</v>
+        <v>24989</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111.7</v>
+        <v>3.43</v>
       </c>
       <c r="B13" t="n">
-        <v>28806</v>
+        <v>36111</v>
       </c>
       <c r="C13" t="n">
-        <v>114.01</v>
+        <v>0.9</v>
       </c>
       <c r="D13" t="n">
-        <v>21260</v>
+        <v>22461</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100.72</v>
+        <v>3.49</v>
       </c>
       <c r="B14" t="n">
-        <v>46166</v>
+        <v>35731</v>
       </c>
       <c r="C14" t="n">
-        <v>102.61</v>
+        <v>0.76</v>
       </c>
       <c r="D14" t="n">
-        <v>29356</v>
+        <v>11897</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91.73999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="B15" t="n">
-        <v>24568</v>
+        <v>36182</v>
       </c>
       <c r="C15" t="n">
-        <v>95.14</v>
+        <v>0.33</v>
       </c>
       <c r="D15" t="n">
-        <v>24717</v>
+        <v>15876</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112.82</v>
+        <v>4.48</v>
       </c>
       <c r="B16" t="n">
-        <v>24562</v>
+        <v>34618</v>
       </c>
       <c r="C16" t="n">
-        <v>116.89</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22596</v>
+        <v>17122</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>92.59</v>
+        <v>4.83</v>
       </c>
       <c r="B17" t="n">
-        <v>26822</v>
+        <v>35729</v>
       </c>
       <c r="C17" t="n">
-        <v>90.03</v>
+        <v>1.43</v>
       </c>
       <c r="D17" t="n">
-        <v>22712</v>
+        <v>18372</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>25.59</v>
+        <v>5.45</v>
       </c>
       <c r="B18" t="n">
-        <v>24322</v>
+        <v>34410</v>
       </c>
       <c r="C18" t="n">
-        <v>25.93</v>
+        <v>5.77</v>
       </c>
       <c r="D18" t="n">
-        <v>23960</v>
+        <v>27090</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97.59</v>
+        <v>5.55</v>
       </c>
       <c r="B19" t="n">
-        <v>40051</v>
+        <v>34717</v>
       </c>
       <c r="C19" t="n">
-        <v>99.98999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="D19" t="n">
-        <v>15355</v>
+        <v>18318</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105.12</v>
+        <v>5.65</v>
       </c>
       <c r="B20" t="n">
-        <v>43256</v>
+        <v>35704</v>
       </c>
       <c r="C20" t="n">
-        <v>105.27</v>
+        <v>2.62</v>
       </c>
       <c r="D20" t="n">
-        <v>29710</v>
+        <v>20991</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>179.06</v>
+        <v>6.77</v>
       </c>
       <c r="B21" t="n">
-        <v>21641</v>
+        <v>34779</v>
       </c>
       <c r="C21" t="n">
-        <v>178.56</v>
+        <v>6.75</v>
       </c>
       <c r="D21" t="n">
-        <v>20502</v>
+        <v>17662</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95.39</v>
+        <v>7.14</v>
       </c>
       <c r="B22" t="n">
-        <v>36924</v>
+        <v>34011</v>
       </c>
       <c r="C22" t="n">
-        <v>92.95999999999999</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>21779</v>
+        <v>15406</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112.69</v>
+        <v>7.97</v>
       </c>
       <c r="B23" t="n">
-        <v>24284</v>
+        <v>32525</v>
       </c>
       <c r="C23" t="n">
-        <v>111.17</v>
+        <v>5.34</v>
       </c>
       <c r="D23" t="n">
-        <v>15903</v>
+        <v>27700</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>93.81</v>
+        <v>8.08</v>
       </c>
       <c r="B24" t="n">
-        <v>28315</v>
+        <v>30862</v>
       </c>
       <c r="C24" t="n">
-        <v>94.56999999999999</v>
+        <v>11.42</v>
       </c>
       <c r="D24" t="n">
-        <v>20265</v>
+        <v>22274</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>100.12</v>
+        <v>8.74</v>
       </c>
       <c r="B25" t="n">
-        <v>43964</v>
+        <v>30784</v>
       </c>
       <c r="C25" t="n">
-        <v>101.79</v>
+        <v>7.77</v>
       </c>
       <c r="D25" t="n">
-        <v>21905</v>
+        <v>17834</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110.03</v>
+        <v>9.81</v>
       </c>
       <c r="B26" t="n">
-        <v>33261</v>
+        <v>29140</v>
       </c>
       <c r="C26" t="n">
-        <v>107.87</v>
+        <v>1.35</v>
       </c>
       <c r="D26" t="n">
-        <v>23229</v>
+        <v>20904</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>92.54000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="B27" t="n">
-        <v>25371</v>
+        <v>30013</v>
       </c>
       <c r="C27" t="n">
-        <v>96.88</v>
+        <v>7.03</v>
       </c>
       <c r="D27" t="n">
-        <v>25707</v>
+        <v>10561</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>92.11</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="B28" t="n">
-        <v>26541</v>
+        <v>31639</v>
       </c>
       <c r="C28" t="n">
-        <v>92.89</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>12777</v>
+        <v>27241</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96.3</v>
+        <v>10.19</v>
       </c>
       <c r="B29" t="n">
-        <v>37437</v>
+        <v>31428</v>
       </c>
       <c r="C29" t="n">
-        <v>98.51000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="D29" t="n">
-        <v>27817</v>
+        <v>18174</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>99.64</v>
+        <v>10.38</v>
       </c>
       <c r="B30" t="n">
-        <v>43312</v>
+        <v>29472</v>
       </c>
       <c r="C30" t="n">
-        <v>97.16</v>
+        <v>8.94</v>
       </c>
       <c r="D30" t="n">
-        <v>12743</v>
+        <v>10804</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>95.83</v>
+        <v>10.4</v>
       </c>
       <c r="B31" t="n">
-        <v>38882</v>
+        <v>30508</v>
       </c>
       <c r="C31" t="n">
-        <v>99.02</v>
+        <v>8.94</v>
       </c>
       <c r="D31" t="n">
-        <v>26954</v>
+        <v>17147</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>110.19</v>
+        <v>11.65</v>
       </c>
       <c r="B32" t="n">
-        <v>33094</v>
+        <v>30266</v>
       </c>
       <c r="C32" t="n">
-        <v>109.5</v>
+        <v>14.44</v>
       </c>
       <c r="D32" t="n">
-        <v>28680</v>
+        <v>27331</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127.04</v>
+        <v>13.05</v>
       </c>
       <c r="B33" t="n">
-        <v>26069</v>
+        <v>29147</v>
       </c>
       <c r="C33" t="n">
-        <v>128.88</v>
+        <v>5.64</v>
       </c>
       <c r="D33" t="n">
-        <v>24386</v>
+        <v>15750</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>106.76</v>
+        <v>13.47</v>
       </c>
       <c r="B34" t="n">
-        <v>43357</v>
+        <v>28528</v>
       </c>
       <c r="C34" t="n">
-        <v>105.33</v>
+        <v>14.02</v>
       </c>
       <c r="D34" t="n">
-        <v>16920</v>
+        <v>24652</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112.89</v>
+        <v>13.76</v>
       </c>
       <c r="B35" t="n">
-        <v>25769</v>
+        <v>27190</v>
       </c>
       <c r="C35" t="n">
-        <v>109.52</v>
+        <v>8.51</v>
       </c>
       <c r="D35" t="n">
-        <v>18108</v>
+        <v>28255</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>106.15</v>
+        <v>14.16</v>
       </c>
       <c r="B36" t="n">
-        <v>41150</v>
+        <v>27008</v>
       </c>
       <c r="C36" t="n">
-        <v>110.09</v>
+        <v>19.03</v>
       </c>
       <c r="D36" t="n">
-        <v>15826</v>
+        <v>21041</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>100.7</v>
+        <v>14.34</v>
       </c>
       <c r="B37" t="n">
-        <v>47712</v>
+        <v>26202</v>
       </c>
       <c r="C37" t="n">
-        <v>101.32</v>
+        <v>7.34</v>
       </c>
       <c r="D37" t="n">
-        <v>25749</v>
+        <v>22641</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>108.09</v>
+        <v>15.02</v>
       </c>
       <c r="B38" t="n">
-        <v>38219</v>
+        <v>23799</v>
       </c>
       <c r="C38" t="n">
-        <v>108.78</v>
+        <v>21.72</v>
       </c>
       <c r="D38" t="n">
-        <v>27293</v>
+        <v>24923</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>92.94</v>
+        <v>15.31</v>
       </c>
       <c r="B39" t="n">
-        <v>29521</v>
+        <v>24155</v>
       </c>
       <c r="C39" t="n">
-        <v>89.66</v>
+        <v>23.29</v>
       </c>
       <c r="D39" t="n">
-        <v>10913</v>
+        <v>23479</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>109.74</v>
+        <v>15.69</v>
       </c>
       <c r="B40" t="n">
-        <v>32779</v>
+        <v>25853</v>
       </c>
       <c r="C40" t="n">
-        <v>114.58</v>
+        <v>17.75</v>
       </c>
       <c r="D40" t="n">
-        <v>24843</v>
+        <v>28786</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113.82</v>
+        <v>16.53</v>
       </c>
       <c r="B41" t="n">
-        <v>23724</v>
+        <v>26465</v>
       </c>
       <c r="C41" t="n">
-        <v>117.29</v>
+        <v>21.05</v>
       </c>
       <c r="D41" t="n">
-        <v>18970</v>
+        <v>14975</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>95.53</v>
+        <v>17.06</v>
       </c>
       <c r="B42" t="n">
-        <v>33547</v>
+        <v>26189</v>
       </c>
       <c r="C42" t="n">
-        <v>97.88</v>
+        <v>22.05</v>
       </c>
       <c r="D42" t="n">
-        <v>15280</v>
+        <v>12929</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>96.03</v>
+        <v>17.46</v>
       </c>
       <c r="B43" t="n">
-        <v>34057</v>
+        <v>25005</v>
       </c>
       <c r="C43" t="n">
-        <v>97.25</v>
+        <v>22.64</v>
       </c>
       <c r="D43" t="n">
-        <v>27875</v>
+        <v>18156</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>106.06</v>
+        <v>17.59</v>
       </c>
       <c r="B44" t="n">
-        <v>43118</v>
+        <v>24630</v>
       </c>
       <c r="C44" t="n">
-        <v>106.32</v>
+        <v>16.09</v>
       </c>
       <c r="D44" t="n">
-        <v>13383</v>
+        <v>22518</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113.28</v>
+        <v>17.79</v>
       </c>
       <c r="B45" t="n">
-        <v>22437</v>
+        <v>26150</v>
       </c>
       <c r="C45" t="n">
-        <v>116.23</v>
+        <v>15.94</v>
       </c>
       <c r="D45" t="n">
-        <v>13521</v>
+        <v>19208</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>107.94</v>
+        <v>17.91</v>
       </c>
       <c r="B46" t="n">
-        <v>38800</v>
+        <v>22816</v>
       </c>
       <c r="C46" t="n">
-        <v>104.28</v>
+        <v>13.24</v>
       </c>
       <c r="D46" t="n">
-        <v>16040</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>107.46</v>
+        <v>18.02</v>
       </c>
       <c r="B47" t="n">
-        <v>38577</v>
+        <v>24874</v>
       </c>
       <c r="C47" t="n">
-        <v>106.32</v>
+        <v>21.23</v>
       </c>
       <c r="D47" t="n">
-        <v>25764</v>
+        <v>24647</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>101.08</v>
+        <v>18.11</v>
       </c>
       <c r="B48" t="n">
-        <v>45894</v>
+        <v>23247</v>
       </c>
       <c r="C48" t="n">
-        <v>100.54</v>
+        <v>18.64</v>
       </c>
       <c r="D48" t="n">
-        <v>10046</v>
+        <v>15637</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>91.05</v>
+        <v>18.15</v>
       </c>
       <c r="B49" t="n">
-        <v>23477</v>
+        <v>24313</v>
       </c>
       <c r="C49" t="n">
-        <v>94.38</v>
+        <v>22.36</v>
       </c>
       <c r="D49" t="n">
-        <v>24105</v>
+        <v>25416</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>114.24</v>
+        <v>18.71</v>
       </c>
       <c r="B50" t="n">
-        <v>24224</v>
+        <v>22615</v>
       </c>
       <c r="C50" t="n">
-        <v>113.45</v>
+        <v>13.99</v>
       </c>
       <c r="D50" t="n">
-        <v>27948</v>
+        <v>10241</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103.12</v>
+        <v>18.87</v>
       </c>
       <c r="B51" t="n">
-        <v>45473</v>
+        <v>24556</v>
       </c>
       <c r="C51" t="n">
-        <v>99.27</v>
+        <v>17.37</v>
       </c>
       <c r="D51" t="n">
-        <v>21546</v>
+        <v>27032</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>96.14</v>
+        <v>19.08</v>
       </c>
       <c r="B52" t="n">
-        <v>37541</v>
+        <v>23956</v>
       </c>
       <c r="C52" t="n">
-        <v>98.19</v>
+        <v>22.42</v>
       </c>
       <c r="D52" t="n">
-        <v>18052</v>
+        <v>15559</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>95.77</v>
+        <v>19.49</v>
       </c>
       <c r="B53" t="n">
-        <v>36102</v>
+        <v>23979</v>
       </c>
       <c r="C53" t="n">
-        <v>92.90000000000001</v>
+        <v>23.3</v>
       </c>
       <c r="D53" t="n">
-        <v>26591</v>
+        <v>23689</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>95.36</v>
+        <v>19.73</v>
       </c>
       <c r="B54" t="n">
-        <v>35121</v>
+        <v>24264</v>
       </c>
       <c r="C54" t="n">
-        <v>93.5</v>
+        <v>19.86</v>
       </c>
       <c r="D54" t="n">
-        <v>12486</v>
+        <v>29129</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>108.89</v>
+        <v>19.86</v>
       </c>
       <c r="B55" t="n">
-        <v>37294</v>
+        <v>22515</v>
       </c>
       <c r="C55" t="n">
-        <v>109.63</v>
+        <v>20.61</v>
       </c>
       <c r="D55" t="n">
-        <v>29427</v>
+        <v>14779</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>90.47</v>
+        <v>20.17</v>
       </c>
       <c r="B56" t="n">
-        <v>26376</v>
+        <v>22922</v>
       </c>
       <c r="C56" t="n">
-        <v>89.48999999999999</v>
+        <v>25.8</v>
       </c>
       <c r="D56" t="n">
-        <v>12255</v>
+        <v>26869</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>109.04</v>
+        <v>20.44</v>
       </c>
       <c r="B57" t="n">
-        <v>34076</v>
+        <v>22256</v>
       </c>
       <c r="C57" t="n">
-        <v>108.69</v>
+        <v>29.52</v>
       </c>
       <c r="D57" t="n">
-        <v>18797</v>
+        <v>29756</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>102.18</v>
+        <v>21.18</v>
       </c>
       <c r="B58" t="n">
-        <v>47157</v>
+        <v>21830</v>
       </c>
       <c r="C58" t="n">
-        <v>102.12</v>
+        <v>23.19</v>
       </c>
       <c r="D58" t="n">
-        <v>21983</v>
+        <v>17112</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>94.53</v>
+        <v>21.27</v>
       </c>
       <c r="B59" t="n">
-        <v>32229</v>
+        <v>23421</v>
       </c>
       <c r="C59" t="n">
-        <v>89.27</v>
+        <v>23.13</v>
       </c>
       <c r="D59" t="n">
-        <v>17181</v>
+        <v>11589</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>90.65000000000001</v>
+        <v>21.51</v>
       </c>
       <c r="B60" t="n">
-        <v>23684</v>
+        <v>24702</v>
       </c>
       <c r="C60" t="n">
-        <v>87.98</v>
+        <v>19.3</v>
       </c>
       <c r="D60" t="n">
-        <v>15184</v>
+        <v>27773</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>105.07</v>
+        <v>21.66</v>
       </c>
       <c r="B61" t="n">
-        <v>46186</v>
+        <v>23598</v>
       </c>
       <c r="C61" t="n">
-        <v>100.77</v>
+        <v>29.03</v>
       </c>
       <c r="D61" t="n">
-        <v>18486</v>
+        <v>23854</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>49.48</v>
+        <v>21.85</v>
       </c>
       <c r="B62" t="n">
-        <v>24642</v>
+        <v>24908</v>
       </c>
       <c r="C62" t="n">
-        <v>48.48</v>
+        <v>15.97</v>
       </c>
       <c r="D62" t="n">
-        <v>17043</v>
+        <v>24483</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>54.01</v>
+        <v>21.98</v>
       </c>
       <c r="B63" t="n">
-        <v>23072</v>
+        <v>22165</v>
       </c>
       <c r="C63" t="n">
-        <v>53.97</v>
+        <v>25.35</v>
       </c>
       <c r="D63" t="n">
-        <v>15479</v>
+        <v>22793</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>114.36</v>
+        <v>22.07</v>
       </c>
       <c r="B64" t="n">
-        <v>24081</v>
+        <v>21342</v>
       </c>
       <c r="C64" t="n">
-        <v>111.51</v>
+        <v>24.65</v>
       </c>
       <c r="D64" t="n">
-        <v>22395</v>
+        <v>19679</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>90.62</v>
+        <v>22.15</v>
       </c>
       <c r="B65" t="n">
-        <v>24964</v>
+        <v>21544</v>
       </c>
       <c r="C65" t="n">
-        <v>90.27</v>
+        <v>22.51</v>
       </c>
       <c r="D65" t="n">
-        <v>28309</v>
+        <v>12311</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>97.45</v>
+        <v>22.49</v>
       </c>
       <c r="B66" t="n">
-        <v>40016</v>
+        <v>23455</v>
       </c>
       <c r="C66" t="n">
-        <v>94.09999999999999</v>
+        <v>30.82</v>
       </c>
       <c r="D66" t="n">
-        <v>11168</v>
+        <v>21596</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>97.47</v>
+        <v>23.14</v>
       </c>
       <c r="B67" t="n">
-        <v>40714</v>
+        <v>24143</v>
       </c>
       <c r="C67" t="n">
-        <v>95.34</v>
+        <v>26.66</v>
       </c>
       <c r="D67" t="n">
-        <v>14905</v>
+        <v>28145</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>151.84</v>
+        <v>23.4</v>
       </c>
       <c r="B68" t="n">
-        <v>22244</v>
+        <v>20768</v>
       </c>
       <c r="C68" t="n">
-        <v>148.21</v>
+        <v>27.97</v>
       </c>
       <c r="D68" t="n">
-        <v>23637</v>
+        <v>12231</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>69.36</v>
+        <v>24</v>
       </c>
       <c r="B69" t="n">
-        <v>24318</v>
+        <v>22893</v>
       </c>
       <c r="C69" t="n">
-        <v>71.55</v>
+        <v>25.19</v>
       </c>
       <c r="D69" t="n">
-        <v>10222</v>
+        <v>13087</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113.11</v>
+        <v>24.2</v>
       </c>
       <c r="B70" t="n">
-        <v>23707</v>
+        <v>21195</v>
       </c>
       <c r="C70" t="n">
-        <v>110.72</v>
+        <v>24.13</v>
       </c>
       <c r="D70" t="n">
-        <v>20963</v>
+        <v>17331</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>114.74</v>
+        <v>25.11</v>
       </c>
       <c r="B71" t="n">
-        <v>22809</v>
+        <v>21977</v>
       </c>
       <c r="C71" t="n">
-        <v>115.35</v>
+        <v>35.82</v>
       </c>
       <c r="D71" t="n">
-        <v>25209</v>
+        <v>26954</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2.12</v>
+        <v>25.72</v>
       </c>
       <c r="B72" t="n">
-        <v>22545</v>
+        <v>22046</v>
       </c>
       <c r="C72" t="n">
-        <v>1.2</v>
+        <v>26.56</v>
       </c>
       <c r="D72" t="n">
-        <v>10712</v>
+        <v>20297</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>111.91</v>
+        <v>25.92</v>
       </c>
       <c r="B73" t="n">
-        <v>27536</v>
+        <v>22107</v>
       </c>
       <c r="C73" t="n">
-        <v>115.03</v>
+        <v>35.21</v>
       </c>
       <c r="D73" t="n">
-        <v>29096</v>
+        <v>23481</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>108.2</v>
+        <v>26.22</v>
       </c>
       <c r="B74" t="n">
-        <v>41737</v>
+        <v>20565</v>
       </c>
       <c r="C74" t="n">
-        <v>112.03</v>
+        <v>27.77</v>
       </c>
       <c r="D74" t="n">
-        <v>20758</v>
+        <v>15294</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>93.88</v>
+        <v>26.87</v>
       </c>
       <c r="B75" t="n">
-        <v>31782</v>
+        <v>21942</v>
       </c>
       <c r="C75" t="n">
-        <v>90.73</v>
+        <v>36</v>
       </c>
       <c r="D75" t="n">
-        <v>29700</v>
+        <v>18761</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>107.6</v>
+        <v>27.38</v>
       </c>
       <c r="B76" t="n">
-        <v>41037</v>
+        <v>20535</v>
       </c>
       <c r="C76" t="n">
-        <v>111.68</v>
+        <v>25.98</v>
       </c>
       <c r="D76" t="n">
-        <v>11232</v>
+        <v>17225</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>91.13</v>
+        <v>27.55</v>
       </c>
       <c r="B77" t="n">
-        <v>25999</v>
+        <v>20456</v>
       </c>
       <c r="C77" t="n">
-        <v>87.90000000000001</v>
+        <v>33.28</v>
       </c>
       <c r="D77" t="n">
-        <v>19258</v>
+        <v>10992</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>110.58</v>
+        <v>27.6</v>
       </c>
       <c r="B78" t="n">
-        <v>28792</v>
+        <v>21912</v>
       </c>
       <c r="C78" t="n">
-        <v>113.81</v>
+        <v>28.77</v>
       </c>
       <c r="D78" t="n">
-        <v>25674</v>
+        <v>22972</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>90.19</v>
+        <v>27.87</v>
       </c>
       <c r="B79" t="n">
-        <v>23318</v>
+        <v>19277</v>
       </c>
       <c r="C79" t="n">
-        <v>93.65000000000001</v>
+        <v>29.65</v>
       </c>
       <c r="D79" t="n">
-        <v>25647</v>
+        <v>14030</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>93.38</v>
+        <v>27.96</v>
       </c>
       <c r="B80" t="n">
-        <v>27791</v>
+        <v>22372</v>
       </c>
       <c r="C80" t="n">
-        <v>92.62</v>
+        <v>26.07</v>
       </c>
       <c r="D80" t="n">
-        <v>21967</v>
+        <v>18021</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>9.19</v>
+        <v>28.27</v>
       </c>
       <c r="B81" t="n">
-        <v>24731</v>
+        <v>19677</v>
       </c>
       <c r="C81" t="n">
-        <v>9.19</v>
+        <v>34.55</v>
       </c>
       <c r="D81" t="n">
-        <v>23845</v>
+        <v>19997</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>95.97</v>
+        <v>28.57</v>
       </c>
       <c r="B82" t="n">
-        <v>33047</v>
+        <v>22549</v>
       </c>
       <c r="C82" t="n">
-        <v>97.42</v>
+        <v>24.54</v>
       </c>
       <c r="D82" t="n">
-        <v>26242</v>
+        <v>22739</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>173.96</v>
+        <v>29.46</v>
       </c>
       <c r="B83" t="n">
-        <v>22994</v>
+        <v>21007</v>
       </c>
       <c r="C83" t="n">
-        <v>175.9</v>
+        <v>30.98</v>
       </c>
       <c r="D83" t="n">
-        <v>27100</v>
+        <v>25156</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>107.38</v>
+        <v>29.66</v>
       </c>
       <c r="B84" t="n">
-        <v>38399</v>
+        <v>21960</v>
       </c>
       <c r="C84" t="n">
-        <v>108.74</v>
+        <v>32.57</v>
       </c>
       <c r="D84" t="n">
-        <v>10667</v>
+        <v>24641</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>92.27</v>
+        <v>30.01</v>
       </c>
       <c r="B85" t="n">
-        <v>27852</v>
+        <v>22195</v>
       </c>
       <c r="C85" t="n">
-        <v>93.56999999999999</v>
+        <v>36.74</v>
       </c>
       <c r="D85" t="n">
-        <v>24916</v>
+        <v>10312</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>97.5</v>
+        <v>30.38</v>
       </c>
       <c r="B86" t="n">
-        <v>38445</v>
+        <v>23678</v>
       </c>
       <c r="C86" t="n">
-        <v>95.75</v>
+        <v>25.12</v>
       </c>
       <c r="D86" t="n">
-        <v>25754</v>
+        <v>21880</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>104.81</v>
+        <v>30.53</v>
       </c>
       <c r="B87" t="n">
-        <v>46714</v>
+        <v>21792</v>
       </c>
       <c r="C87" t="n">
-        <v>100.31</v>
+        <v>26.48</v>
       </c>
       <c r="D87" t="n">
-        <v>12450</v>
+        <v>29285</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>92</v>
+        <v>30.86</v>
       </c>
       <c r="B88" t="n">
-        <v>25884</v>
+        <v>21938</v>
       </c>
       <c r="C88" t="n">
-        <v>93.23</v>
+        <v>28.24</v>
       </c>
       <c r="D88" t="n">
-        <v>16018</v>
+        <v>16136</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>103.3</v>
+        <v>31.48</v>
       </c>
       <c r="B89" t="n">
-        <v>45169</v>
+        <v>22832</v>
       </c>
       <c r="C89" t="n">
-        <v>100.55</v>
+        <v>29.95</v>
       </c>
       <c r="D89" t="n">
-        <v>18350</v>
+        <v>19099</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>106.52</v>
+        <v>31.63</v>
       </c>
       <c r="B90" t="n">
-        <v>42508</v>
+        <v>23572</v>
       </c>
       <c r="C90" t="n">
-        <v>105.93</v>
+        <v>29.06</v>
       </c>
       <c r="D90" t="n">
-        <v>11653</v>
+        <v>26360</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>99</v>
+        <v>32.55</v>
       </c>
       <c r="B91" t="n">
-        <v>41143</v>
+        <v>21562</v>
       </c>
       <c r="C91" t="n">
-        <v>99.23</v>
+        <v>37.46</v>
       </c>
       <c r="D91" t="n">
-        <v>14855</v>
+        <v>28609</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>97.03</v>
+        <v>33.07</v>
       </c>
       <c r="B92" t="n">
-        <v>40575</v>
+        <v>21389</v>
       </c>
       <c r="C92" t="n">
-        <v>92.69</v>
+        <v>34.57</v>
       </c>
       <c r="D92" t="n">
-        <v>27070</v>
+        <v>29417</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>175.28</v>
+        <v>33.1</v>
       </c>
       <c r="B93" t="n">
-        <v>21316</v>
+        <v>18074</v>
       </c>
       <c r="C93" t="n">
-        <v>180</v>
+        <v>31.47</v>
       </c>
       <c r="D93" t="n">
-        <v>23069</v>
+        <v>24739</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>102.39</v>
+        <v>33.31</v>
       </c>
       <c r="B94" t="n">
-        <v>46825</v>
+        <v>21138</v>
       </c>
       <c r="C94" t="n">
-        <v>103.65</v>
+        <v>38.76</v>
       </c>
       <c r="D94" t="n">
-        <v>19859</v>
+        <v>17573</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>105.65</v>
+        <v>34.04</v>
       </c>
       <c r="B95" t="n">
-        <v>42024</v>
+        <v>22018</v>
       </c>
       <c r="C95" t="n">
-        <v>104.19</v>
+        <v>25.57</v>
       </c>
       <c r="D95" t="n">
-        <v>20298</v>
+        <v>14412</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>110.21</v>
+        <v>34.32</v>
       </c>
       <c r="B96" t="n">
-        <v>31961</v>
+        <v>21715</v>
       </c>
       <c r="C96" t="n">
-        <v>108.72</v>
+        <v>49.11</v>
       </c>
       <c r="D96" t="n">
-        <v>12791</v>
+        <v>20017</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>93.25</v>
+        <v>35.3</v>
       </c>
       <c r="B97" t="n">
-        <v>29572</v>
+        <v>21713</v>
       </c>
       <c r="C97" t="n">
-        <v>92.87</v>
+        <v>40.92</v>
       </c>
       <c r="D97" t="n">
-        <v>12954</v>
+        <v>17577</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>103.17</v>
+        <v>35.64</v>
       </c>
       <c r="B98" t="n">
-        <v>48126</v>
+        <v>20222</v>
       </c>
       <c r="C98" t="n">
-        <v>103.98</v>
+        <v>25.72</v>
       </c>
       <c r="D98" t="n">
-        <v>24609</v>
+        <v>20243</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>94.53</v>
+        <v>35.68</v>
       </c>
       <c r="B99" t="n">
-        <v>30478</v>
+        <v>20484</v>
       </c>
       <c r="C99" t="n">
-        <v>92.11</v>
+        <v>31.92</v>
       </c>
       <c r="D99" t="n">
-        <v>22671</v>
+        <v>13725</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>25.98</v>
+        <v>36.88</v>
       </c>
       <c r="B100" t="n">
-        <v>24267</v>
+        <v>20641</v>
       </c>
       <c r="C100" t="n">
-        <v>25.92</v>
+        <v>23.87</v>
       </c>
       <c r="D100" t="n">
-        <v>18023</v>
+        <v>28390</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>109.79</v>
+        <v>37.03</v>
       </c>
       <c r="B101" t="n">
-        <v>31934</v>
+        <v>22575</v>
       </c>
       <c r="C101" t="n">
-        <v>111.01</v>
+        <v>35.69</v>
       </c>
       <c r="D101" t="n">
-        <v>16933</v>
+        <v>11432</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>113.19</v>
+        <v>38.13</v>
       </c>
       <c r="B102" t="n">
-        <v>22913</v>
+        <v>18682</v>
       </c>
       <c r="C102" t="n">
-        <v>116.28</v>
+        <v>41.36</v>
       </c>
       <c r="D102" t="n">
-        <v>22564</v>
+        <v>27086</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>104.01</v>
+        <v>38.83</v>
       </c>
       <c r="B103" t="n">
-        <v>44181</v>
+        <v>21900</v>
       </c>
       <c r="C103" t="n">
-        <v>101.37</v>
+        <v>35.38</v>
       </c>
       <c r="D103" t="n">
-        <v>27861</v>
+        <v>18810</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>107.8</v>
+        <v>38.85</v>
       </c>
       <c r="B104" t="n">
-        <v>38059</v>
+        <v>19393</v>
       </c>
       <c r="C104" t="n">
-        <v>110.92</v>
+        <v>37.84</v>
       </c>
       <c r="D104" t="n">
-        <v>23048</v>
+        <v>24339</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>104.82</v>
+        <v>39.05</v>
       </c>
       <c r="B105" t="n">
-        <v>43894</v>
+        <v>22334</v>
       </c>
       <c r="C105" t="n">
-        <v>101.65</v>
+        <v>49.67</v>
       </c>
       <c r="D105" t="n">
-        <v>23622</v>
+        <v>29296</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>91.75</v>
+        <v>39.8</v>
       </c>
       <c r="B106" t="n">
-        <v>26998</v>
+        <v>21440</v>
       </c>
       <c r="C106" t="n">
-        <v>90.77</v>
+        <v>41.37</v>
       </c>
       <c r="D106" t="n">
-        <v>23312</v>
+        <v>26829</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>105.97</v>
+        <v>41.34</v>
       </c>
       <c r="B107" t="n">
-        <v>44142</v>
+        <v>18477</v>
       </c>
       <c r="C107" t="n">
-        <v>105.19</v>
+        <v>46.46</v>
       </c>
       <c r="D107" t="n">
-        <v>25725</v>
+        <v>12059</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>106.99</v>
+        <v>41.65</v>
       </c>
       <c r="B108" t="n">
-        <v>42157</v>
+        <v>19168</v>
       </c>
       <c r="C108" t="n">
-        <v>109.53</v>
+        <v>40.27</v>
       </c>
       <c r="D108" t="n">
-        <v>20017</v>
+        <v>15115</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>95.78</v>
+        <v>42.09</v>
       </c>
       <c r="B109" t="n">
-        <v>35849</v>
+        <v>17676</v>
       </c>
       <c r="C109" t="n">
-        <v>94.78</v>
+        <v>36.6</v>
       </c>
       <c r="D109" t="n">
-        <v>15261</v>
+        <v>18680</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>55.38</v>
+        <v>42.44</v>
       </c>
       <c r="B110" t="n">
-        <v>23762</v>
+        <v>21906</v>
       </c>
       <c r="C110" t="n">
-        <v>55.6</v>
+        <v>45.92</v>
       </c>
       <c r="D110" t="n">
-        <v>20922</v>
+        <v>17562</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>114.09</v>
+        <v>42.5</v>
       </c>
       <c r="B111" t="n">
-        <v>22128</v>
+        <v>19521</v>
       </c>
       <c r="C111" t="n">
-        <v>117.9</v>
+        <v>43.33</v>
       </c>
       <c r="D111" t="n">
-        <v>25466</v>
+        <v>19472</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>95.2</v>
+        <v>43.28</v>
       </c>
       <c r="B112" t="n">
-        <v>35343</v>
+        <v>21518</v>
       </c>
       <c r="C112" t="n">
-        <v>97.73999999999999</v>
+        <v>32.56</v>
       </c>
       <c r="D112" t="n">
-        <v>21566</v>
+        <v>14119</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>95.17</v>
+        <v>43.9</v>
       </c>
       <c r="B113" t="n">
-        <v>36905</v>
+        <v>18591</v>
       </c>
       <c r="C113" t="n">
-        <v>94.34</v>
+        <v>31.81</v>
       </c>
       <c r="D113" t="n">
-        <v>22148</v>
+        <v>12151</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>96.65000000000001</v>
+        <v>44.08</v>
       </c>
       <c r="B114" t="n">
-        <v>39524</v>
+        <v>18952</v>
       </c>
       <c r="C114" t="n">
-        <v>98.15000000000001</v>
+        <v>35.95</v>
       </c>
       <c r="D114" t="n">
-        <v>11929</v>
+        <v>20340</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>103.33</v>
+        <v>44.38</v>
       </c>
       <c r="B115" t="n">
-        <v>47479</v>
+        <v>21080</v>
       </c>
       <c r="C115" t="n">
-        <v>106.31</v>
+        <v>43.87</v>
       </c>
       <c r="D115" t="n">
-        <v>25289</v>
+        <v>13836</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>111.96</v>
+        <v>44.87</v>
       </c>
       <c r="B116" t="n">
-        <v>29445</v>
+        <v>22384</v>
       </c>
       <c r="C116" t="n">
-        <v>115.24</v>
+        <v>50.7</v>
       </c>
       <c r="D116" t="n">
-        <v>28618</v>
+        <v>18613</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>109.62</v>
+        <v>45.22</v>
       </c>
       <c r="B117" t="n">
-        <v>31605</v>
+        <v>21248</v>
       </c>
       <c r="C117" t="n">
-        <v>109.35</v>
+        <v>40.55</v>
       </c>
       <c r="D117" t="n">
-        <v>29481</v>
+        <v>26191</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>89.31</v>
+        <v>45.83</v>
       </c>
       <c r="B118" t="n">
-        <v>21930</v>
+        <v>22838</v>
       </c>
       <c r="C118" t="n">
-        <v>88.98</v>
+        <v>42.83</v>
       </c>
       <c r="D118" t="n">
-        <v>20041</v>
+        <v>27363</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>91.48999999999999</v>
+        <v>45.9</v>
       </c>
       <c r="B119" t="n">
-        <v>24629</v>
+        <v>23719</v>
       </c>
       <c r="C119" t="n">
-        <v>89.93000000000001</v>
+        <v>52.86</v>
       </c>
       <c r="D119" t="n">
-        <v>10814</v>
+        <v>14079</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>93.94</v>
+        <v>46.51</v>
       </c>
       <c r="B120" t="n">
-        <v>30510</v>
+        <v>20313</v>
       </c>
       <c r="C120" t="n">
-        <v>95.38</v>
+        <v>47.69</v>
       </c>
       <c r="D120" t="n">
-        <v>12447</v>
+        <v>11987</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>113.47</v>
+        <v>47.47</v>
       </c>
       <c r="B121" t="n">
-        <v>25525</v>
+        <v>21354</v>
       </c>
       <c r="C121" t="n">
-        <v>110.21</v>
+        <v>40.52</v>
       </c>
       <c r="D121" t="n">
-        <v>15444</v>
+        <v>28765</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>102.75</v>
+        <v>48.75</v>
       </c>
       <c r="B122" t="n">
-        <v>44577</v>
+        <v>18388</v>
       </c>
       <c r="C122" t="n">
-        <v>106.31</v>
+        <v>51.22</v>
       </c>
       <c r="D122" t="n">
-        <v>29624</v>
+        <v>21703</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>63.44</v>
+        <v>48.89</v>
       </c>
       <c r="B123" t="n">
-        <v>23034</v>
+        <v>21717</v>
       </c>
       <c r="C123" t="n">
-        <v>62.06</v>
+        <v>52.5</v>
       </c>
       <c r="D123" t="n">
-        <v>15830</v>
+        <v>17133</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>101.86</v>
+        <v>49.34</v>
       </c>
       <c r="B124" t="n">
-        <v>46642</v>
+        <v>19165</v>
       </c>
       <c r="C124" t="n">
-        <v>101.63</v>
+        <v>51.42</v>
       </c>
       <c r="D124" t="n">
-        <v>28955</v>
+        <v>18921</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>100.14</v>
+        <v>49.47</v>
       </c>
       <c r="B125" t="n">
-        <v>45895</v>
+        <v>19417</v>
       </c>
       <c r="C125" t="n">
-        <v>97.02</v>
+        <v>55.66</v>
       </c>
       <c r="D125" t="n">
-        <v>14685</v>
+        <v>12281</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>112.79</v>
+        <v>49.5</v>
       </c>
       <c r="B126" t="n">
-        <v>23239</v>
+        <v>21097</v>
       </c>
       <c r="C126" t="n">
-        <v>114.04</v>
+        <v>51.9</v>
       </c>
       <c r="D126" t="n">
-        <v>13311</v>
+        <v>18690</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>108.09</v>
+        <v>50.84</v>
       </c>
       <c r="B127" t="n">
-        <v>34217</v>
+        <v>22467</v>
       </c>
       <c r="C127" t="n">
-        <v>108.63</v>
+        <v>57.3</v>
       </c>
       <c r="D127" t="n">
-        <v>26985</v>
+        <v>12778</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>113.32</v>
+        <v>51.81</v>
       </c>
       <c r="B128" t="n">
-        <v>25105</v>
+        <v>20451</v>
       </c>
       <c r="C128" t="n">
-        <v>112.09</v>
+        <v>37.04</v>
       </c>
       <c r="D128" t="n">
-        <v>14120</v>
+        <v>10971</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>167.53</v>
+        <v>51.93</v>
       </c>
       <c r="B129" t="n">
-        <v>21824</v>
+        <v>20580</v>
       </c>
       <c r="C129" t="n">
-        <v>162.33</v>
+        <v>49.18</v>
       </c>
       <c r="D129" t="n">
-        <v>20685</v>
+        <v>13852</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>114.49</v>
+        <v>52.16</v>
       </c>
       <c r="B130" t="n">
-        <v>24204</v>
+        <v>20223</v>
       </c>
       <c r="C130" t="n">
-        <v>116.03</v>
+        <v>52.78</v>
       </c>
       <c r="D130" t="n">
-        <v>18141</v>
+        <v>24385</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>94.28</v>
+        <v>52.49</v>
       </c>
       <c r="B131" t="n">
-        <v>31210</v>
+        <v>23217</v>
       </c>
       <c r="C131" t="n">
-        <v>93.26000000000001</v>
+        <v>44.03</v>
       </c>
       <c r="D131" t="n">
-        <v>21931</v>
+        <v>27081</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>110.43</v>
+        <v>52.58</v>
       </c>
       <c r="B132" t="n">
-        <v>32034</v>
+        <v>21264</v>
       </c>
       <c r="C132" t="n">
-        <v>106.15</v>
+        <v>41.42</v>
       </c>
       <c r="D132" t="n">
-        <v>15042</v>
+        <v>24593</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>123.27</v>
+        <v>54.08</v>
       </c>
       <c r="B133" t="n">
-        <v>21726</v>
+        <v>20792</v>
       </c>
       <c r="C133" t="n">
-        <v>117.78</v>
+        <v>58.63</v>
       </c>
       <c r="D133" t="n">
-        <v>24249</v>
+        <v>21586</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>101.79</v>
+        <v>54.15</v>
       </c>
       <c r="B134" t="n">
-        <v>47749</v>
+        <v>22716</v>
       </c>
       <c r="C134" t="n">
-        <v>101.71</v>
+        <v>38.16</v>
       </c>
       <c r="D134" t="n">
-        <v>26876</v>
+        <v>16718</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>47.11</v>
+        <v>54.2</v>
       </c>
       <c r="B135" t="n">
-        <v>23491</v>
+        <v>22157</v>
       </c>
       <c r="C135" t="n">
-        <v>47.16</v>
+        <v>62.75</v>
       </c>
       <c r="D135" t="n">
-        <v>15339</v>
+        <v>19398</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>100.94</v>
+        <v>54.5</v>
       </c>
       <c r="B136" t="n">
-        <v>46368</v>
+        <v>20330</v>
       </c>
       <c r="C136" t="n">
-        <v>98.68000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="D136" t="n">
-        <v>26095</v>
+        <v>29404</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>24.04</v>
+        <v>54.88</v>
       </c>
       <c r="B137" t="n">
-        <v>24186</v>
+        <v>22641</v>
       </c>
       <c r="C137" t="n">
-        <v>24.34</v>
+        <v>54.52</v>
       </c>
       <c r="D137" t="n">
-        <v>27312</v>
+        <v>20060</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>110.41</v>
+        <v>54.97</v>
       </c>
       <c r="B138" t="n">
-        <v>31030</v>
+        <v>20821</v>
       </c>
       <c r="C138" t="n">
-        <v>109.58</v>
+        <v>63.26</v>
       </c>
       <c r="D138" t="n">
-        <v>27389</v>
+        <v>29838</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>93.8</v>
+        <v>54.98</v>
       </c>
       <c r="B139" t="n">
-        <v>29273</v>
+        <v>19302</v>
       </c>
       <c r="C139" t="n">
-        <v>94.95999999999999</v>
+        <v>56.01</v>
       </c>
       <c r="D139" t="n">
-        <v>10600</v>
+        <v>29763</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>110.8</v>
+        <v>55.13</v>
       </c>
       <c r="B140" t="n">
-        <v>29158</v>
+        <v>19962</v>
       </c>
       <c r="C140" t="n">
-        <v>107.79</v>
+        <v>56.28</v>
       </c>
       <c r="D140" t="n">
-        <v>28125</v>
+        <v>17395</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>32.09</v>
+        <v>55.41</v>
       </c>
       <c r="B141" t="n">
-        <v>21163</v>
+        <v>22344</v>
       </c>
       <c r="C141" t="n">
-        <v>32.62</v>
+        <v>40.7</v>
       </c>
       <c r="D141" t="n">
-        <v>12584</v>
+        <v>10854</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>74.95</v>
+        <v>55.51</v>
       </c>
       <c r="B142" t="n">
-        <v>24022</v>
+        <v>20882</v>
       </c>
       <c r="C142" t="n">
-        <v>77.66</v>
+        <v>59.87</v>
       </c>
       <c r="D142" t="n">
-        <v>20517</v>
+        <v>10815</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>98.22</v>
+        <v>55.69</v>
       </c>
       <c r="B143" t="n">
-        <v>40446</v>
+        <v>20315</v>
       </c>
       <c r="C143" t="n">
-        <v>96.98</v>
+        <v>45.87</v>
       </c>
       <c r="D143" t="n">
-        <v>26749</v>
+        <v>28298</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>91.64</v>
+        <v>56.06</v>
       </c>
       <c r="B144" t="n">
-        <v>26984</v>
+        <v>20241</v>
       </c>
       <c r="C144" t="n">
-        <v>91.54000000000001</v>
+        <v>42.57</v>
       </c>
       <c r="D144" t="n">
-        <v>29982</v>
+        <v>21071</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>95.86</v>
+        <v>56.58</v>
       </c>
       <c r="B145" t="n">
-        <v>36847</v>
+        <v>21964</v>
       </c>
       <c r="C145" t="n">
-        <v>98.17</v>
+        <v>49.24</v>
       </c>
       <c r="D145" t="n">
-        <v>22365</v>
+        <v>29650</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>104.36</v>
+        <v>57.53</v>
       </c>
       <c r="B146" t="n">
-        <v>49304</v>
+        <v>20307</v>
       </c>
       <c r="C146" t="n">
-        <v>103.2</v>
+        <v>54.01</v>
       </c>
       <c r="D146" t="n">
-        <v>26045</v>
+        <v>20042</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>136.79</v>
+        <v>57.62</v>
       </c>
       <c r="B147" t="n">
-        <v>24613</v>
+        <v>20010</v>
       </c>
       <c r="C147" t="n">
-        <v>134.08</v>
+        <v>63.15</v>
       </c>
       <c r="D147" t="n">
-        <v>26553</v>
+        <v>26545</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>106.56</v>
+        <v>58.12</v>
       </c>
       <c r="B148" t="n">
-        <v>42206</v>
+        <v>22662</v>
       </c>
       <c r="C148" t="n">
-        <v>103.57</v>
+        <v>48.76</v>
       </c>
       <c r="D148" t="n">
-        <v>29562</v>
+        <v>28810</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>110.54</v>
+        <v>58.22</v>
       </c>
       <c r="B149" t="n">
-        <v>29956</v>
+        <v>19820</v>
       </c>
       <c r="C149" t="n">
-        <v>106.76</v>
+        <v>67.09</v>
       </c>
       <c r="D149" t="n">
-        <v>16930</v>
+        <v>21930</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>107.33</v>
+        <v>58.39</v>
       </c>
       <c r="B150" t="n">
-        <v>42152</v>
+        <v>20715</v>
       </c>
       <c r="C150" t="n">
-        <v>110.62</v>
+        <v>56.3</v>
       </c>
       <c r="D150" t="n">
-        <v>26166</v>
+        <v>12178</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>101.73</v>
+        <v>58.43</v>
       </c>
       <c r="B151" t="n">
-        <v>46706</v>
+        <v>20658</v>
       </c>
       <c r="C151" t="n">
-        <v>98.97</v>
+        <v>67.58</v>
       </c>
       <c r="D151" t="n">
-        <v>28771</v>
+        <v>29016</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>103.99</v>
+        <v>58.55</v>
       </c>
       <c r="B152" t="n">
-        <v>45410</v>
+        <v>22436</v>
       </c>
       <c r="C152" t="n">
-        <v>102.15</v>
+        <v>58.74</v>
       </c>
       <c r="D152" t="n">
-        <v>29497</v>
+        <v>27349</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>95.7</v>
+        <v>58.99</v>
       </c>
       <c r="B153" t="n">
-        <v>34645</v>
+        <v>21410</v>
       </c>
       <c r="C153" t="n">
-        <v>96.31</v>
+        <v>55.83</v>
       </c>
       <c r="D153" t="n">
-        <v>10116</v>
+        <v>20772</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>112.5</v>
+        <v>59.93</v>
       </c>
       <c r="B154" t="n">
-        <v>24798</v>
+        <v>19660</v>
       </c>
       <c r="C154" t="n">
-        <v>114.36</v>
+        <v>58.93</v>
       </c>
       <c r="D154" t="n">
-        <v>19938</v>
+        <v>18676</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>92.77</v>
+        <v>59.93</v>
       </c>
       <c r="B155" t="n">
-        <v>28727</v>
+        <v>20764</v>
       </c>
       <c r="C155" t="n">
-        <v>93.90000000000001</v>
+        <v>50.93</v>
       </c>
       <c r="D155" t="n">
-        <v>15639</v>
+        <v>25439</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>91.89</v>
+        <v>59.99</v>
       </c>
       <c r="B156" t="n">
-        <v>27358</v>
+        <v>20831</v>
       </c>
       <c r="C156" t="n">
-        <v>94.41</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D156" t="n">
-        <v>14996</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>114.37</v>
+        <v>60.07</v>
       </c>
       <c r="B157" t="n">
-        <v>27130</v>
+        <v>19929</v>
       </c>
       <c r="C157" t="n">
-        <v>117.22</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="D157" t="n">
-        <v>10226</v>
+        <v>16133</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>92.5</v>
+        <v>60.59</v>
       </c>
       <c r="B158" t="n">
-        <v>25636</v>
+        <v>20815</v>
       </c>
       <c r="C158" t="n">
-        <v>94.06</v>
+        <v>68.42</v>
       </c>
       <c r="D158" t="n">
-        <v>14279</v>
+        <v>18199</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>100</v>
+        <v>60.86</v>
       </c>
       <c r="B159" t="n">
-        <v>40210</v>
+        <v>18953</v>
       </c>
       <c r="C159" t="n">
-        <v>102.98</v>
+        <v>51.1</v>
       </c>
       <c r="D159" t="n">
-        <v>20280</v>
+        <v>27578</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>94.79000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="B160" t="n">
-        <v>33162</v>
+        <v>20358</v>
       </c>
       <c r="C160" t="n">
-        <v>95.43000000000001</v>
+        <v>67.34</v>
       </c>
       <c r="D160" t="n">
-        <v>19542</v>
+        <v>13450</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>105.55</v>
+        <v>61.44</v>
       </c>
       <c r="B161" t="n">
-        <v>42535</v>
+        <v>21416</v>
       </c>
       <c r="C161" t="n">
-        <v>109.29</v>
+        <v>41.09</v>
       </c>
       <c r="D161" t="n">
-        <v>21076</v>
+        <v>26366</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>113.11</v>
+        <v>62.21</v>
       </c>
       <c r="B162" t="n">
-        <v>27302</v>
+        <v>23216</v>
       </c>
       <c r="C162" t="n">
-        <v>115.35</v>
+        <v>67.91</v>
       </c>
       <c r="D162" t="n">
-        <v>27136</v>
+        <v>27986</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>109.65</v>
+        <v>62.24</v>
       </c>
       <c r="B163" t="n">
-        <v>35491</v>
+        <v>21297</v>
       </c>
       <c r="C163" t="n">
-        <v>110.68</v>
+        <v>75.41</v>
       </c>
       <c r="D163" t="n">
-        <v>24581</v>
+        <v>27130</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>97.54000000000001</v>
+        <v>62.41</v>
       </c>
       <c r="B164" t="n">
-        <v>39546</v>
+        <v>21640</v>
       </c>
       <c r="C164" t="n">
-        <v>101.06</v>
+        <v>59.06</v>
       </c>
       <c r="D164" t="n">
-        <v>14236</v>
+        <v>23893</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>98.09</v>
+        <v>63.66</v>
       </c>
       <c r="B165" t="n">
-        <v>43858</v>
+        <v>19670</v>
       </c>
       <c r="C165" t="n">
-        <v>95.84999999999999</v>
+        <v>60.6</v>
       </c>
       <c r="D165" t="n">
-        <v>15981</v>
+        <v>20513</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>90.17</v>
+        <v>63.93</v>
       </c>
       <c r="B166" t="n">
-        <v>21765</v>
+        <v>20367</v>
       </c>
       <c r="C166" t="n">
-        <v>89.37</v>
+        <v>56.34</v>
       </c>
       <c r="D166" t="n">
-        <v>29719</v>
+        <v>29762</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>93.67</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="B167" t="n">
-        <v>27910</v>
+        <v>19169</v>
       </c>
       <c r="C167" t="n">
-        <v>95.11</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="D167" t="n">
-        <v>19190</v>
+        <v>28599</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>107.88</v>
+        <v>64.78</v>
       </c>
       <c r="B168" t="n">
-        <v>36281</v>
+        <v>21979</v>
       </c>
       <c r="C168" t="n">
-        <v>107.71</v>
+        <v>76.53</v>
       </c>
       <c r="D168" t="n">
-        <v>14326</v>
+        <v>20138</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>90.75</v>
+        <v>65.05</v>
       </c>
       <c r="B169" t="n">
-        <v>23862</v>
+        <v>19684</v>
       </c>
       <c r="C169" t="n">
-        <v>87.89</v>
+        <v>56.33</v>
       </c>
       <c r="D169" t="n">
-        <v>14836</v>
+        <v>21751</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>108.9</v>
+        <v>65.38</v>
       </c>
       <c r="B170" t="n">
-        <v>34511</v>
+        <v>20582</v>
       </c>
       <c r="C170" t="n">
-        <v>107.6</v>
+        <v>57.42</v>
       </c>
       <c r="D170" t="n">
-        <v>15541</v>
+        <v>11390</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>0.58</v>
+        <v>65.42</v>
       </c>
       <c r="B171" t="n">
-        <v>22966</v>
+        <v>19186</v>
       </c>
       <c r="C171" t="n">
-        <v>0.49</v>
+        <v>71.09</v>
       </c>
       <c r="D171" t="n">
-        <v>24793</v>
+        <v>11995</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>150.69</v>
+        <v>65.52</v>
       </c>
       <c r="B172" t="n">
-        <v>26404</v>
+        <v>20438</v>
       </c>
       <c r="C172" t="n">
-        <v>153.66</v>
+        <v>55.45</v>
       </c>
       <c r="D172" t="n">
-        <v>11484</v>
+        <v>17494</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>97.61</v>
+        <v>66.33</v>
       </c>
       <c r="B173" t="n">
-        <v>37996</v>
+        <v>19306</v>
       </c>
       <c r="C173" t="n">
-        <v>94.08</v>
+        <v>56.51</v>
       </c>
       <c r="D173" t="n">
-        <v>23502</v>
+        <v>11030</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>111.56</v>
+        <v>66.34</v>
       </c>
       <c r="B174" t="n">
-        <v>27924</v>
+        <v>20250</v>
       </c>
       <c r="C174" t="n">
-        <v>107</v>
+        <v>63.46</v>
       </c>
       <c r="D174" t="n">
-        <v>12924</v>
+        <v>25170</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>102.94</v>
+        <v>66.36</v>
       </c>
       <c r="B175" t="n">
-        <v>47627</v>
+        <v>20437</v>
       </c>
       <c r="C175" t="n">
-        <v>105.27</v>
+        <v>77</v>
       </c>
       <c r="D175" t="n">
-        <v>21051</v>
+        <v>12843</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>113.34</v>
+        <v>66.41</v>
       </c>
       <c r="B176" t="n">
-        <v>23307</v>
+        <v>19715</v>
       </c>
       <c r="C176" t="n">
-        <v>117.22</v>
+        <v>50.58</v>
       </c>
       <c r="D176" t="n">
-        <v>27749</v>
+        <v>18185</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>107.64</v>
+        <v>66.81</v>
       </c>
       <c r="B177" t="n">
-        <v>39760</v>
+        <v>21217</v>
       </c>
       <c r="C177" t="n">
-        <v>110.71</v>
+        <v>49.7</v>
       </c>
       <c r="D177" t="n">
-        <v>25515</v>
+        <v>28203</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>22.85</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="B178" t="n">
-        <v>23554</v>
+        <v>21064</v>
       </c>
       <c r="C178" t="n">
-        <v>21.22</v>
+        <v>64.64</v>
       </c>
       <c r="D178" t="n">
-        <v>21280</v>
+        <v>12099</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>102.77</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="B179" t="n">
-        <v>47133</v>
+        <v>19647</v>
       </c>
       <c r="C179" t="n">
-        <v>100.81</v>
+        <v>59.43</v>
       </c>
       <c r="D179" t="n">
-        <v>29289</v>
+        <v>24929</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>111.07</v>
+        <v>67.77</v>
       </c>
       <c r="B180" t="n">
-        <v>29730</v>
+        <v>21250</v>
       </c>
       <c r="C180" t="n">
-        <v>113.38</v>
+        <v>49.72</v>
       </c>
       <c r="D180" t="n">
-        <v>29413</v>
+        <v>18790</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131.44</v>
+        <v>68.09</v>
       </c>
       <c r="B181" t="n">
-        <v>23654</v>
+        <v>20163</v>
       </c>
       <c r="C181" t="n">
-        <v>127.44</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="D181" t="n">
-        <v>18889</v>
+        <v>29038</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>145.8</v>
+        <v>68.37</v>
       </c>
       <c r="B182" t="n">
-        <v>24954</v>
+        <v>21336</v>
       </c>
       <c r="C182" t="n">
-        <v>143.12</v>
+        <v>83.69</v>
       </c>
       <c r="D182" t="n">
-        <v>20669</v>
+        <v>14858</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>101.21</v>
+        <v>68.63</v>
       </c>
       <c r="B183" t="n">
-        <v>45173</v>
+        <v>20322</v>
       </c>
       <c r="C183" t="n">
-        <v>97.51000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="D183" t="n">
-        <v>10474</v>
+        <v>16421</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>102.29</v>
+        <v>68.73</v>
       </c>
       <c r="B184" t="n">
-        <v>44837</v>
+        <v>19572</v>
       </c>
       <c r="C184" t="n">
-        <v>104.39</v>
+        <v>55.07</v>
       </c>
       <c r="D184" t="n">
-        <v>10536</v>
+        <v>18822</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>92.17</v>
+        <v>69.19</v>
       </c>
       <c r="B185" t="n">
-        <v>26321</v>
+        <v>19674</v>
       </c>
       <c r="C185" t="n">
-        <v>95.42</v>
+        <v>58.73</v>
       </c>
       <c r="D185" t="n">
-        <v>23657</v>
+        <v>21567</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>96.34999999999999</v>
+        <v>69.67</v>
       </c>
       <c r="B186" t="n">
-        <v>38318</v>
+        <v>20530</v>
       </c>
       <c r="C186" t="n">
-        <v>94.44</v>
+        <v>76.27</v>
       </c>
       <c r="D186" t="n">
-        <v>17834</v>
+        <v>21025</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>105.89</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="B187" t="n">
-        <v>44997</v>
+        <v>20370</v>
       </c>
       <c r="C187" t="n">
-        <v>103.49</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="D187" t="n">
-        <v>26771</v>
+        <v>10056</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>104.86</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="B188" t="n">
-        <v>46563</v>
+        <v>21103</v>
       </c>
       <c r="C188" t="n">
-        <v>105.73</v>
+        <v>60.51</v>
       </c>
       <c r="D188" t="n">
-        <v>18960</v>
+        <v>20906</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>58.07</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="B189" t="n">
-        <v>21940</v>
+        <v>21191</v>
       </c>
       <c r="C189" t="n">
-        <v>57.78</v>
+        <v>67.45</v>
       </c>
       <c r="D189" t="n">
-        <v>10056</v>
+        <v>16071</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>111.15</v>
+        <v>70.27</v>
       </c>
       <c r="B190" t="n">
-        <v>27256</v>
+        <v>20250</v>
       </c>
       <c r="C190" t="n">
-        <v>107.87</v>
+        <v>68.44</v>
       </c>
       <c r="D190" t="n">
-        <v>11239</v>
+        <v>16011</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>147.15</v>
+        <v>70.38</v>
       </c>
       <c r="B191" t="n">
-        <v>19646</v>
+        <v>19036</v>
       </c>
       <c r="C191" t="n">
-        <v>146.83</v>
+        <v>73.47</v>
       </c>
       <c r="D191" t="n">
-        <v>15686</v>
+        <v>10389</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>112.81</v>
+        <v>70.44</v>
       </c>
       <c r="B192" t="n">
-        <v>25598</v>
+        <v>21585</v>
       </c>
       <c r="C192" t="n">
-        <v>112.68</v>
+        <v>62.06</v>
       </c>
       <c r="D192" t="n">
-        <v>18343</v>
+        <v>11427</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>105.96</v>
+        <v>70.89</v>
       </c>
       <c r="B193" t="n">
-        <v>43352</v>
+        <v>19065</v>
       </c>
       <c r="C193" t="n">
-        <v>107.72</v>
+        <v>58.38</v>
       </c>
       <c r="D193" t="n">
-        <v>28314</v>
+        <v>27868</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>104.85</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="B194" t="n">
-        <v>46865</v>
+        <v>19225</v>
       </c>
       <c r="C194" t="n">
-        <v>104.84</v>
+        <v>63.6</v>
       </c>
       <c r="D194" t="n">
-        <v>29064</v>
+        <v>17868</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>107.77</v>
+        <v>71.41</v>
       </c>
       <c r="B195" t="n">
-        <v>40391</v>
+        <v>20570</v>
       </c>
       <c r="C195" t="n">
-        <v>105.74</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="D195" t="n">
-        <v>25092</v>
+        <v>27625</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>95.29000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="B196" t="n">
-        <v>34788</v>
+        <v>20944</v>
       </c>
       <c r="C196" t="n">
-        <v>98.89</v>
+        <v>80.62</v>
       </c>
       <c r="D196" t="n">
-        <v>13037</v>
+        <v>24813</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>179.71</v>
+        <v>72</v>
       </c>
       <c r="B197" t="n">
-        <v>23844</v>
+        <v>20639</v>
       </c>
       <c r="C197" t="n">
-        <v>180</v>
+        <v>83.19</v>
       </c>
       <c r="D197" t="n">
-        <v>28397</v>
+        <v>12244</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>100.15</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="B198" t="n">
-        <v>44677</v>
+        <v>19846</v>
       </c>
       <c r="C198" t="n">
-        <v>99.8</v>
+        <v>73.25</v>
       </c>
       <c r="D198" t="n">
-        <v>18767</v>
+        <v>11115</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>114.44</v>
+        <v>72.47</v>
       </c>
       <c r="B199" t="n">
-        <v>23280</v>
+        <v>20316</v>
       </c>
       <c r="C199" t="n">
-        <v>117.55</v>
+        <v>61.03</v>
       </c>
       <c r="D199" t="n">
-        <v>12679</v>
+        <v>17739</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>109.66</v>
+        <v>72.5</v>
       </c>
       <c r="B200" t="n">
-        <v>33067</v>
+        <v>19496</v>
       </c>
       <c r="C200" t="n">
-        <v>111.38</v>
+        <v>73.39</v>
       </c>
       <c r="D200" t="n">
-        <v>13146</v>
+        <v>14782</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>113.14</v>
+        <v>72.81</v>
       </c>
       <c r="B201" t="n">
-        <v>26081</v>
+        <v>21072</v>
       </c>
       <c r="C201" t="n">
-        <v>108.42</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="D201" t="n">
-        <v>28886</v>
+        <v>28156</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>18.2</v>
+        <v>73.38</v>
       </c>
       <c r="B202" t="n">
-        <v>26658</v>
+        <v>20464</v>
       </c>
       <c r="C202" t="n">
-        <v>18.12</v>
+        <v>75.22</v>
       </c>
       <c r="D202" t="n">
-        <v>26746</v>
+        <v>24479</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>93.44</v>
+        <v>73.66</v>
       </c>
       <c r="B203" t="n">
-        <v>26463</v>
+        <v>19907</v>
       </c>
       <c r="C203" t="n">
-        <v>97.05</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="D203" t="n">
-        <v>19462</v>
+        <v>12448</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>113.05</v>
+        <v>74.16</v>
       </c>
       <c r="B204" t="n">
-        <v>24990</v>
+        <v>20361</v>
       </c>
       <c r="C204" t="n">
-        <v>112.91</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="D204" t="n">
-        <v>18877</v>
+        <v>22780</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>32.43</v>
+        <v>74.36</v>
       </c>
       <c r="B205" t="n">
-        <v>24046</v>
+        <v>19831</v>
       </c>
       <c r="C205" t="n">
-        <v>32.67</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="D205" t="n">
-        <v>25203</v>
+        <v>11271</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>114.36</v>
+        <v>74.73</v>
       </c>
       <c r="B206" t="n">
-        <v>25200</v>
+        <v>21824</v>
       </c>
       <c r="C206" t="n">
-        <v>115.52</v>
+        <v>62.01</v>
       </c>
       <c r="D206" t="n">
-        <v>15891</v>
+        <v>20305</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>110.2</v>
+        <v>75.53</v>
       </c>
       <c r="B207" t="n">
-        <v>34090</v>
+        <v>21402</v>
       </c>
       <c r="C207" t="n">
-        <v>113.72</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="D207" t="n">
-        <v>28750</v>
+        <v>17974</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>111.58</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="B208" t="n">
-        <v>29450</v>
+        <v>22626</v>
       </c>
       <c r="C208" t="n">
-        <v>106.84</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D208" t="n">
-        <v>11128</v>
+        <v>24205</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>108.4</v>
+        <v>76.22</v>
       </c>
       <c r="B209" t="n">
-        <v>39378</v>
+        <v>20491</v>
       </c>
       <c r="C209" t="n">
-        <v>104.69</v>
+        <v>77.95</v>
       </c>
       <c r="D209" t="n">
-        <v>28124</v>
+        <v>26256</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>101.1</v>
+        <v>76.36</v>
       </c>
       <c r="B210" t="n">
-        <v>44911</v>
+        <v>20086</v>
       </c>
       <c r="C210" t="n">
-        <v>97.45999999999999</v>
+        <v>55.68</v>
       </c>
       <c r="D210" t="n">
-        <v>15553</v>
+        <v>16468</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>96.17</v>
+        <v>76.81</v>
       </c>
       <c r="B211" t="n">
-        <v>38654</v>
+        <v>20661</v>
       </c>
       <c r="C211" t="n">
-        <v>99.36</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D211" t="n">
-        <v>20045</v>
+        <v>13687</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>114.59</v>
+        <v>76.84</v>
       </c>
       <c r="B212" t="n">
-        <v>21678</v>
+        <v>20753</v>
       </c>
       <c r="C212" t="n">
-        <v>116.53</v>
+        <v>89.3</v>
       </c>
       <c r="D212" t="n">
-        <v>21804</v>
+        <v>16067</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127.47</v>
+        <v>77.09</v>
       </c>
       <c r="B213" t="n">
-        <v>22279</v>
+        <v>21136</v>
       </c>
       <c r="C213" t="n">
-        <v>123.64</v>
+        <v>89.62</v>
       </c>
       <c r="D213" t="n">
-        <v>27537</v>
+        <v>16995</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>96.3</v>
+        <v>77.37</v>
       </c>
       <c r="B214" t="n">
-        <v>39133</v>
+        <v>20697</v>
       </c>
       <c r="C214" t="n">
-        <v>93.8</v>
+        <v>72.58</v>
       </c>
       <c r="D214" t="n">
-        <v>29252</v>
+        <v>20124</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>75.33</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="B215" t="n">
-        <v>23509</v>
+        <v>21013</v>
       </c>
       <c r="C215" t="n">
-        <v>72.41</v>
+        <v>65.89</v>
       </c>
       <c r="D215" t="n">
-        <v>22642</v>
+        <v>26552</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>106.74</v>
+        <v>78.03</v>
       </c>
       <c r="B216" t="n">
-        <v>43505</v>
+        <v>20184</v>
       </c>
       <c r="C216" t="n">
-        <v>110.16</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="D216" t="n">
-        <v>14750</v>
+        <v>13906</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>105.76</v>
+        <v>78.25</v>
       </c>
       <c r="B217" t="n">
-        <v>45386</v>
+        <v>21098</v>
       </c>
       <c r="C217" t="n">
-        <v>107.34</v>
+        <v>70.8</v>
       </c>
       <c r="D217" t="n">
-        <v>25962</v>
+        <v>22309</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>101.93</v>
+        <v>78.33</v>
       </c>
       <c r="B218" t="n">
-        <v>45307</v>
+        <v>20296</v>
       </c>
       <c r="C218" t="n">
-        <v>99.44</v>
+        <v>101.87</v>
       </c>
       <c r="D218" t="n">
-        <v>14637</v>
+        <v>10117</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>110.37</v>
+        <v>78.52</v>
       </c>
       <c r="B219" t="n">
-        <v>29717</v>
+        <v>21265</v>
       </c>
       <c r="C219" t="n">
-        <v>107.35</v>
+        <v>92.55</v>
       </c>
       <c r="D219" t="n">
-        <v>29514</v>
+        <v>29238</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>15.89</v>
+        <v>79.06</v>
       </c>
       <c r="B220" t="n">
-        <v>21773</v>
+        <v>20198</v>
       </c>
       <c r="C220" t="n">
-        <v>13.84</v>
+        <v>88.5</v>
       </c>
       <c r="D220" t="n">
-        <v>19065</v>
+        <v>27019</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>105.13</v>
+        <v>80.25</v>
       </c>
       <c r="B221" t="n">
-        <v>42707</v>
+        <v>21625</v>
       </c>
       <c r="C221" t="n">
-        <v>105.33</v>
+        <v>94.17</v>
       </c>
       <c r="D221" t="n">
-        <v>17359</v>
+        <v>18280</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>92.23999999999999</v>
+        <v>80.75</v>
       </c>
       <c r="B222" t="n">
-        <v>27015</v>
+        <v>19995</v>
       </c>
       <c r="C222" t="n">
-        <v>92.89</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D222" t="n">
-        <v>16131</v>
+        <v>22766</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>108.45</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="B223" t="n">
-        <v>38730</v>
+        <v>20122</v>
       </c>
       <c r="C223" t="n">
-        <v>105.88</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="D223" t="n">
-        <v>16477</v>
+        <v>29856</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>99.84999999999999</v>
+        <v>82.12</v>
       </c>
       <c r="B224" t="n">
-        <v>44378</v>
+        <v>20930</v>
       </c>
       <c r="C224" t="n">
-        <v>104.05</v>
+        <v>90.38</v>
       </c>
       <c r="D224" t="n">
-        <v>25037</v>
+        <v>10795</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>90.79000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="B225" t="n">
-        <v>22304</v>
+        <v>20383</v>
       </c>
       <c r="C225" t="n">
-        <v>90.31999999999999</v>
+        <v>78.91</v>
       </c>
       <c r="D225" t="n">
-        <v>20983</v>
+        <v>12740</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>113.55</v>
+        <v>82.44</v>
       </c>
       <c r="B226" t="n">
-        <v>24559</v>
+        <v>19998</v>
       </c>
       <c r="C226" t="n">
-        <v>115.76</v>
+        <v>80.61</v>
       </c>
       <c r="D226" t="n">
-        <v>13880</v>
+        <v>28612</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>94.26000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="B227" t="n">
-        <v>29954</v>
+        <v>19832</v>
       </c>
       <c r="C227" t="n">
-        <v>93.62</v>
+        <v>59.15</v>
       </c>
       <c r="D227" t="n">
-        <v>12703</v>
+        <v>19818</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127.96</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="B228" t="n">
-        <v>24421</v>
+        <v>20881</v>
       </c>
       <c r="C228" t="n">
-        <v>127.93</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D228" t="n">
-        <v>21127</v>
+        <v>23151</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>105.06</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="B229" t="n">
-        <v>44780</v>
+        <v>20391</v>
       </c>
       <c r="C229" t="n">
-        <v>107.21</v>
+        <v>87.81</v>
       </c>
       <c r="D229" t="n">
-        <v>17813</v>
+        <v>21732</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>101.89</v>
+        <v>83.53</v>
       </c>
       <c r="B230" t="n">
-        <v>47775</v>
+        <v>20912</v>
       </c>
       <c r="C230" t="n">
-        <v>97.97</v>
+        <v>76.17</v>
       </c>
       <c r="D230" t="n">
-        <v>18734</v>
+        <v>23073</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>156.69</v>
+        <v>84.5</v>
       </c>
       <c r="B231" t="n">
-        <v>25459</v>
+        <v>19992</v>
       </c>
       <c r="C231" t="n">
-        <v>150.49</v>
+        <v>89.02</v>
       </c>
       <c r="D231" t="n">
-        <v>19150</v>
+        <v>13073</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>111.55</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="B232" t="n">
-        <v>30770</v>
+        <v>19523</v>
       </c>
       <c r="C232" t="n">
-        <v>110.02</v>
+        <v>76.3</v>
       </c>
       <c r="D232" t="n">
-        <v>19567</v>
+        <v>20165</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>92.2</v>
+        <v>84.75</v>
       </c>
       <c r="B233" t="n">
-        <v>26504</v>
+        <v>19705</v>
       </c>
       <c r="C233" t="n">
-        <v>95.34</v>
+        <v>71.87</v>
       </c>
       <c r="D233" t="n">
-        <v>10078</v>
+        <v>20655</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>110.79</v>
+        <v>84.95</v>
       </c>
       <c r="B234" t="n">
-        <v>26781</v>
+        <v>18358</v>
       </c>
       <c r="C234" t="n">
-        <v>108.58</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="D234" t="n">
-        <v>27335</v>
+        <v>23468</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>103.42</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="B235" t="n">
-        <v>45438</v>
+        <v>20275</v>
       </c>
       <c r="C235" t="n">
-        <v>99.84</v>
+        <v>87.2</v>
       </c>
       <c r="D235" t="n">
-        <v>20410</v>
+        <v>12706</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>106.9</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="B236" t="n">
-        <v>41181</v>
+        <v>19616</v>
       </c>
       <c r="C236" t="n">
-        <v>103.9</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="D236" t="n">
-        <v>14474</v>
+        <v>25822</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>112.48</v>
+        <v>85.63</v>
       </c>
       <c r="B237" t="n">
-        <v>24109</v>
+        <v>20863</v>
       </c>
       <c r="C237" t="n">
-        <v>108.48</v>
+        <v>84.75</v>
       </c>
       <c r="D237" t="n">
-        <v>29981</v>
+        <v>22058</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>114.87</v>
+        <v>86.23</v>
       </c>
       <c r="B238" t="n">
-        <v>23823</v>
+        <v>20449</v>
       </c>
       <c r="C238" t="n">
-        <v>115.79</v>
+        <v>73.19</v>
       </c>
       <c r="D238" t="n">
-        <v>24061</v>
+        <v>15305</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>94.84</v>
+        <v>86.78</v>
       </c>
       <c r="B239" t="n">
-        <v>33597</v>
+        <v>20472</v>
       </c>
       <c r="C239" t="n">
-        <v>94.59999999999999</v>
+        <v>80.34</v>
       </c>
       <c r="D239" t="n">
-        <v>11036</v>
+        <v>10815</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>99.75</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="B240" t="n">
-        <v>43385</v>
+        <v>21035</v>
       </c>
       <c r="C240" t="n">
-        <v>98.39</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="D240" t="n">
-        <v>23096</v>
+        <v>25646</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>96.41</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="B241" t="n">
-        <v>39177</v>
+        <v>19813</v>
       </c>
       <c r="C241" t="n">
-        <v>99.3</v>
+        <v>96.83</v>
       </c>
       <c r="D241" t="n">
-        <v>18880</v>
+        <v>12274</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>98.91</v>
+        <v>88.63</v>
       </c>
       <c r="B242" t="n">
-        <v>42117</v>
+        <v>19977</v>
       </c>
       <c r="C242" t="n">
-        <v>100.51</v>
+        <v>102.04</v>
       </c>
       <c r="D242" t="n">
-        <v>14209</v>
+        <v>12021</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>106.81</v>
+        <v>88.77</v>
       </c>
       <c r="B243" t="n">
-        <v>41065</v>
+        <v>21071</v>
       </c>
       <c r="C243" t="n">
-        <v>101.91</v>
+        <v>93.53</v>
       </c>
       <c r="D243" t="n">
-        <v>15521</v>
+        <v>12009</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>92.62</v>
+        <v>89.06</v>
       </c>
       <c r="B244" t="n">
-        <v>25655</v>
+        <v>21306</v>
       </c>
       <c r="C244" t="n">
-        <v>94.52</v>
+        <v>78.7</v>
       </c>
       <c r="D244" t="n">
-        <v>29969</v>
+        <v>22008</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>41.52</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="B245" t="n">
-        <v>25086</v>
+        <v>21148</v>
       </c>
       <c r="C245" t="n">
-        <v>42.26</v>
+        <v>95.31</v>
       </c>
       <c r="D245" t="n">
-        <v>25535</v>
+        <v>27267</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>96.89</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="B246" t="n">
-        <v>38523</v>
+        <v>20850</v>
       </c>
       <c r="C246" t="n">
-        <v>96.69</v>
+        <v>104.43</v>
       </c>
       <c r="D246" t="n">
-        <v>13851</v>
+        <v>15961</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>96.77</v>
+        <v>89.84</v>
       </c>
       <c r="B247" t="n">
-        <v>39531</v>
+        <v>20697</v>
       </c>
       <c r="C247" t="n">
-        <v>93.53</v>
+        <v>75.95</v>
       </c>
       <c r="D247" t="n">
-        <v>27354</v>
+        <v>23682</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>105.46</v>
+        <v>89.86</v>
       </c>
       <c r="B248" t="n">
-        <v>45004</v>
+        <v>20133</v>
       </c>
       <c r="C248" t="n">
-        <v>103.71</v>
+        <v>103.28</v>
       </c>
       <c r="D248" t="n">
-        <v>12611</v>
+        <v>26905</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>35.12</v>
+        <v>90.48</v>
       </c>
       <c r="B249" t="n">
-        <v>21481</v>
+        <v>21585</v>
       </c>
       <c r="C249" t="n">
-        <v>33.93</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D249" t="n">
-        <v>12997</v>
+        <v>17856</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>110.07</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="B250" t="n">
-        <v>34345</v>
+        <v>21512</v>
       </c>
       <c r="C250" t="n">
-        <v>110.22</v>
+        <v>73.73</v>
       </c>
       <c r="D250" t="n">
-        <v>20601</v>
+        <v>16023</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>126.39</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="B251" t="n">
-        <v>21591</v>
+        <v>21699</v>
       </c>
       <c r="C251" t="n">
-        <v>124.72</v>
+        <v>93.28</v>
       </c>
       <c r="D251" t="n">
-        <v>28093</v>
+        <v>27403</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>100.96</v>
+        <v>91.06</v>
       </c>
       <c r="B252" t="n">
-        <v>47659</v>
+        <v>21078</v>
       </c>
       <c r="C252" t="n">
-        <v>98.68000000000001</v>
+        <v>76.64</v>
       </c>
       <c r="D252" t="n">
-        <v>27200</v>
+        <v>14492</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>108.88</v>
+        <v>91.25</v>
       </c>
       <c r="B253" t="n">
-        <v>33131</v>
+        <v>20747</v>
       </c>
       <c r="C253" t="n">
-        <v>104.66</v>
+        <v>103.08</v>
       </c>
       <c r="D253" t="n">
-        <v>21130</v>
+        <v>25294</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>112.62</v>
+        <v>91.67</v>
       </c>
       <c r="B254" t="n">
-        <v>27655</v>
+        <v>20993</v>
       </c>
       <c r="C254" t="n">
-        <v>108.75</v>
+        <v>69.98</v>
       </c>
       <c r="D254" t="n">
-        <v>19557</v>
+        <v>16905</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>99.56999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="B255" t="n">
-        <v>43902</v>
+        <v>20529</v>
       </c>
       <c r="C255" t="n">
-        <v>99.67</v>
+        <v>94.58</v>
       </c>
       <c r="D255" t="n">
-        <v>19976</v>
+        <v>27264</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>102.02</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="B256" t="n">
-        <v>48065</v>
+        <v>22176</v>
       </c>
       <c r="C256" t="n">
-        <v>103.15</v>
+        <v>106.22</v>
       </c>
       <c r="D256" t="n">
-        <v>10878</v>
+        <v>21057</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>103.6</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="B257" t="n">
-        <v>46493</v>
+        <v>21320</v>
       </c>
       <c r="C257" t="n">
-        <v>107.27</v>
+        <v>101.49</v>
       </c>
       <c r="D257" t="n">
-        <v>24683</v>
+        <v>12681</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>94.81</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="B258" t="n">
-        <v>35938</v>
+        <v>23197</v>
       </c>
       <c r="C258" t="n">
-        <v>97.58</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="D258" t="n">
-        <v>23779</v>
+        <v>29370</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>73.47</v>
+        <v>92.92</v>
       </c>
       <c r="B259" t="n">
-        <v>24004</v>
+        <v>22757</v>
       </c>
       <c r="C259" t="n">
-        <v>72.47</v>
+        <v>81.03</v>
       </c>
       <c r="D259" t="n">
-        <v>24510</v>
+        <v>10486</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>105</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="B260" t="n">
-        <v>45309</v>
+        <v>22981</v>
       </c>
       <c r="C260" t="n">
-        <v>108.12</v>
+        <v>79.77</v>
       </c>
       <c r="D260" t="n">
-        <v>20404</v>
+        <v>21216</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>111.1</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="B261" t="n">
-        <v>31061</v>
+        <v>23425</v>
       </c>
       <c r="C261" t="n">
-        <v>111.72</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="D261" t="n">
-        <v>16816</v>
+        <v>20712</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>64.86</v>
+        <v>94.55</v>
       </c>
       <c r="B262" t="n">
-        <v>23071</v>
+        <v>24233</v>
       </c>
       <c r="C262" t="n">
-        <v>63</v>
+        <v>88.17</v>
       </c>
       <c r="D262" t="n">
-        <v>15413</v>
+        <v>23080</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>114.25</v>
+        <v>94.73</v>
       </c>
       <c r="B263" t="n">
-        <v>24423</v>
+        <v>24570</v>
       </c>
       <c r="C263" t="n">
-        <v>112.09</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="D263" t="n">
-        <v>14315</v>
+        <v>26982</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>94.09</v>
+        <v>94.89</v>
       </c>
       <c r="B264" t="n">
-        <v>32022</v>
+        <v>25482</v>
       </c>
       <c r="C264" t="n">
-        <v>90.33</v>
+        <v>82.08</v>
       </c>
       <c r="D264" t="n">
-        <v>23352</v>
+        <v>12434</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>111.61</v>
+        <v>95.25</v>
       </c>
       <c r="B265" t="n">
-        <v>30133</v>
+        <v>25703</v>
       </c>
       <c r="C265" t="n">
-        <v>109.49</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="D265" t="n">
-        <v>13984</v>
+        <v>12721</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>109.73</v>
+        <v>96.31</v>
       </c>
       <c r="B266" t="n">
-        <v>32573</v>
+        <v>27314</v>
       </c>
       <c r="C266" t="n">
-        <v>109.22</v>
+        <v>113.96</v>
       </c>
       <c r="D266" t="n">
-        <v>13050</v>
+        <v>26538</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>100.72</v>
+        <v>97.14</v>
       </c>
       <c r="B267" t="n">
-        <v>44398</v>
+        <v>29028</v>
       </c>
       <c r="C267" t="n">
-        <v>99.52</v>
+        <v>111.78</v>
       </c>
       <c r="D267" t="n">
-        <v>25926</v>
+        <v>16496</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>100.07</v>
+        <v>97.38</v>
       </c>
       <c r="B268" t="n">
-        <v>44458</v>
+        <v>30120</v>
       </c>
       <c r="C268" t="n">
-        <v>101.61</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="D268" t="n">
-        <v>17910</v>
+        <v>21454</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>51.35</v>
+        <v>97.59</v>
       </c>
       <c r="B269" t="n">
-        <v>22743</v>
+        <v>29874</v>
       </c>
       <c r="C269" t="n">
-        <v>52.84</v>
+        <v>94.36</v>
       </c>
       <c r="D269" t="n">
-        <v>23334</v>
+        <v>28197</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>91.72</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="B270" t="n">
-        <v>24192</v>
+        <v>30515</v>
       </c>
       <c r="C270" t="n">
-        <v>90.25</v>
+        <v>103.77</v>
       </c>
       <c r="D270" t="n">
-        <v>21201</v>
+        <v>28998</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>99.41</v>
+        <v>97.89</v>
       </c>
       <c r="B271" t="n">
-        <v>42478</v>
+        <v>31145</v>
       </c>
       <c r="C271" t="n">
-        <v>97.23</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="D271" t="n">
-        <v>26869</v>
+        <v>24063</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>107.99</v>
+        <v>98.59</v>
       </c>
       <c r="B272" t="n">
-        <v>38512</v>
+        <v>32592</v>
       </c>
       <c r="C272" t="n">
-        <v>107.83</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D272" t="n">
-        <v>29197</v>
+        <v>22001</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>92.59999999999999</v>
+        <v>98.84</v>
       </c>
       <c r="B273" t="n">
-        <v>30486</v>
+        <v>32671</v>
       </c>
       <c r="C273" t="n">
-        <v>93.81</v>
+        <v>109.3</v>
       </c>
       <c r="D273" t="n">
-        <v>23610</v>
+        <v>22736</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>107.79</v>
+        <v>98.98</v>
       </c>
       <c r="B274" t="n">
-        <v>37985</v>
+        <v>31879</v>
       </c>
       <c r="C274" t="n">
-        <v>107.01</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D274" t="n">
-        <v>20156</v>
+        <v>16143</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>110.03</v>
+        <v>99.92</v>
       </c>
       <c r="B275" t="n">
-        <v>33268</v>
+        <v>35027</v>
       </c>
       <c r="C275" t="n">
-        <v>113.53</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D275" t="n">
-        <v>28087</v>
+        <v>21809</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>103.21</v>
+        <v>99.98</v>
       </c>
       <c r="B276" t="n">
-        <v>48233</v>
+        <v>35383</v>
       </c>
       <c r="C276" t="n">
-        <v>103.02</v>
+        <v>116.36</v>
       </c>
       <c r="D276" t="n">
-        <v>11366</v>
+        <v>24984</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>97.8</v>
+        <v>100.62</v>
       </c>
       <c r="B277" t="n">
-        <v>38403</v>
+        <v>36090</v>
       </c>
       <c r="C277" t="n">
-        <v>98.09</v>
+        <v>122.52</v>
       </c>
       <c r="D277" t="n">
-        <v>29586</v>
+        <v>25854</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>141.74</v>
+        <v>100.78</v>
       </c>
       <c r="B278" t="n">
-        <v>22817</v>
+        <v>36759</v>
       </c>
       <c r="C278" t="n">
-        <v>139.75</v>
+        <v>102.2</v>
       </c>
       <c r="D278" t="n">
-        <v>21388</v>
+        <v>14819</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>99.11</v>
+        <v>100.89</v>
       </c>
       <c r="B279" t="n">
-        <v>47580</v>
+        <v>36566</v>
       </c>
       <c r="C279" t="n">
-        <v>96.43000000000001</v>
+        <v>102.59</v>
       </c>
       <c r="D279" t="n">
-        <v>11691</v>
+        <v>19878</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>119.05</v>
+        <v>101.72</v>
       </c>
       <c r="B280" t="n">
-        <v>22839</v>
+        <v>37137</v>
       </c>
       <c r="C280" t="n">
-        <v>121.46</v>
+        <v>112.75</v>
       </c>
       <c r="D280" t="n">
-        <v>23923</v>
+        <v>14243</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>12.58</v>
+        <v>101.92</v>
       </c>
       <c r="B281" t="n">
-        <v>25760</v>
+        <v>37781</v>
       </c>
       <c r="C281" t="n">
-        <v>12.52</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="D281" t="n">
-        <v>19239</v>
+        <v>26523</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>112.37</v>
+        <v>102.39</v>
       </c>
       <c r="B282" t="n">
-        <v>26648</v>
+        <v>37219</v>
       </c>
       <c r="C282" t="n">
-        <v>110.97</v>
+        <v>115.13</v>
       </c>
       <c r="D282" t="n">
-        <v>23613</v>
+        <v>10751</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>94.04000000000001</v>
+        <v>102.41</v>
       </c>
       <c r="B283" t="n">
-        <v>31312</v>
+        <v>37076</v>
       </c>
       <c r="C283" t="n">
-        <v>90.77</v>
+        <v>99.16</v>
       </c>
       <c r="D283" t="n">
-        <v>16314</v>
+        <v>25920</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>99.77</v>
+        <v>103</v>
       </c>
       <c r="B284" t="n">
-        <v>44792</v>
+        <v>37880</v>
       </c>
       <c r="C284" t="n">
-        <v>102.58</v>
+        <v>79.25</v>
       </c>
       <c r="D284" t="n">
-        <v>27683</v>
+        <v>15571</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>108.25</v>
+        <v>103.49</v>
       </c>
       <c r="B285" t="n">
-        <v>37278</v>
+        <v>37688</v>
       </c>
       <c r="C285" t="n">
-        <v>107.1</v>
+        <v>99.38</v>
       </c>
       <c r="D285" t="n">
-        <v>12502</v>
+        <v>21788</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>111.08</v>
+        <v>104.54</v>
       </c>
       <c r="B286" t="n">
-        <v>29662</v>
+        <v>36496</v>
       </c>
       <c r="C286" t="n">
-        <v>113.46</v>
+        <v>110.59</v>
       </c>
       <c r="D286" t="n">
-        <v>21839</v>
+        <v>19308</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>170.97</v>
+        <v>105.24</v>
       </c>
       <c r="B287" t="n">
-        <v>22415</v>
+        <v>35453</v>
       </c>
       <c r="C287" t="n">
-        <v>174.12</v>
+        <v>129.07</v>
       </c>
       <c r="D287" t="n">
-        <v>22107</v>
+        <v>14008</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>92.81</v>
+        <v>105.45</v>
       </c>
       <c r="B288" t="n">
-        <v>26024</v>
+        <v>36427</v>
       </c>
       <c r="C288" t="n">
-        <v>93.14</v>
+        <v>106.07</v>
       </c>
       <c r="D288" t="n">
-        <v>21485</v>
+        <v>25853</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>103.43</v>
+        <v>105.48</v>
       </c>
       <c r="B289" t="n">
-        <v>49733</v>
+        <v>36395</v>
       </c>
       <c r="C289" t="n">
-        <v>103.23</v>
+        <v>96.44</v>
       </c>
       <c r="D289" t="n">
-        <v>13252</v>
+        <v>16371</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>106.58</v>
+        <v>105.77</v>
       </c>
       <c r="B290" t="n">
-        <v>42671</v>
+        <v>35347</v>
       </c>
       <c r="C290" t="n">
-        <v>106.98</v>
+        <v>107.43</v>
       </c>
       <c r="D290" t="n">
-        <v>10657</v>
+        <v>20388</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>105.63</v>
+        <v>105.98</v>
       </c>
       <c r="B291" t="n">
-        <v>45209</v>
+        <v>35289</v>
       </c>
       <c r="C291" t="n">
-        <v>107.75</v>
+        <v>119.77</v>
       </c>
       <c r="D291" t="n">
-        <v>11550</v>
+        <v>18974</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>87.23999999999999</v>
+        <v>106.17</v>
       </c>
       <c r="B292" t="n">
-        <v>21453</v>
+        <v>34513</v>
       </c>
       <c r="C292" t="n">
-        <v>88.88</v>
+        <v>102.05</v>
       </c>
       <c r="D292" t="n">
-        <v>12566</v>
+        <v>23935</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>114.34</v>
+        <v>106.35</v>
       </c>
       <c r="B293" t="n">
-        <v>22511</v>
+        <v>35016</v>
       </c>
       <c r="C293" t="n">
-        <v>117.73</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="D293" t="n">
-        <v>24149</v>
+        <v>16059</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>90.25</v>
+        <v>106.66</v>
       </c>
       <c r="B294" t="n">
-        <v>23862</v>
+        <v>33808</v>
       </c>
       <c r="C294" t="n">
-        <v>92.04000000000001</v>
+        <v>90.72</v>
       </c>
       <c r="D294" t="n">
-        <v>10605</v>
+        <v>19840</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>94.17</v>
+        <v>108.39</v>
       </c>
       <c r="B295" t="n">
-        <v>31533</v>
+        <v>29912</v>
       </c>
       <c r="C295" t="n">
-        <v>97.39</v>
+        <v>105.22</v>
       </c>
       <c r="D295" t="n">
-        <v>12900</v>
+        <v>18623</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>114.36</v>
+        <v>108.43</v>
       </c>
       <c r="B296" t="n">
-        <v>22848</v>
+        <v>29156</v>
       </c>
       <c r="C296" t="n">
-        <v>115.88</v>
+        <v>105.73</v>
       </c>
       <c r="D296" t="n">
-        <v>29313</v>
+        <v>20002</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>6.08</v>
+        <v>108.48</v>
       </c>
       <c r="B297" t="n">
-        <v>22166</v>
+        <v>30233</v>
       </c>
       <c r="C297" t="n">
-        <v>5.66</v>
+        <v>108.58</v>
       </c>
       <c r="D297" t="n">
-        <v>18931</v>
+        <v>17148</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>97.58</v>
+        <v>109.77</v>
       </c>
       <c r="B298" t="n">
-        <v>38129</v>
+        <v>26386</v>
       </c>
       <c r="C298" t="n">
-        <v>95.18000000000001</v>
+        <v>80.98</v>
       </c>
       <c r="D298" t="n">
-        <v>11796</v>
+        <v>12808</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>103.28</v>
+        <v>111</v>
       </c>
       <c r="B299" t="n">
-        <v>46907</v>
+        <v>25758</v>
       </c>
       <c r="C299" t="n">
-        <v>102.32</v>
+        <v>104.67</v>
       </c>
       <c r="D299" t="n">
-        <v>22773</v>
+        <v>22408</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>105.61</v>
+        <v>111.17</v>
       </c>
       <c r="B300" t="n">
-        <v>46076</v>
+        <v>25423</v>
       </c>
       <c r="C300" t="n">
-        <v>109.61</v>
+        <v>104.75</v>
       </c>
       <c r="D300" t="n">
-        <v>24794</v>
+        <v>29915</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>93.56999999999999</v>
+        <v>111.33</v>
       </c>
       <c r="B301" t="n">
-        <v>30588</v>
+        <v>24834</v>
       </c>
       <c r="C301" t="n">
-        <v>91.7</v>
+        <v>135.19</v>
       </c>
       <c r="D301" t="n">
-        <v>28386</v>
+        <v>18356</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>110.68</v>
+        <v>112.14</v>
       </c>
       <c r="B302" t="n">
-        <v>33458</v>
+        <v>23722</v>
       </c>
       <c r="C302" t="n">
-        <v>107.52</v>
+        <v>117.22</v>
       </c>
       <c r="D302" t="n">
-        <v>17838</v>
+        <v>27341</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>5.97</v>
+        <v>112.17</v>
       </c>
       <c r="B303" t="n">
-        <v>22314</v>
+        <v>23598</v>
       </c>
       <c r="C303" t="n">
-        <v>7.03</v>
+        <v>101.74</v>
       </c>
       <c r="D303" t="n">
-        <v>27893</v>
+        <v>26582</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>104.37</v>
+        <v>112.17</v>
       </c>
       <c r="B304" t="n">
-        <v>46431</v>
+        <v>22267</v>
       </c>
       <c r="C304" t="n">
-        <v>104.56</v>
+        <v>135.16</v>
       </c>
       <c r="D304" t="n">
-        <v>15045</v>
+        <v>21711</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>97.18000000000001</v>
+        <v>112.18</v>
       </c>
       <c r="B305" t="n">
-        <v>42333</v>
+        <v>21691</v>
       </c>
       <c r="C305" t="n">
-        <v>97.61</v>
+        <v>104.52</v>
       </c>
       <c r="D305" t="n">
-        <v>27230</v>
+        <v>11488</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>110.09</v>
+        <v>112.2</v>
       </c>
       <c r="B306" t="n">
-        <v>32894</v>
+        <v>20866</v>
       </c>
       <c r="C306" t="n">
-        <v>106.39</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="D306" t="n">
-        <v>21329</v>
+        <v>20157</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>107</v>
+        <v>112.21</v>
       </c>
       <c r="B307" t="n">
-        <v>40484</v>
+        <v>22165</v>
       </c>
       <c r="C307" t="n">
-        <v>103.56</v>
+        <v>135.27</v>
       </c>
       <c r="D307" t="n">
-        <v>13656</v>
+        <v>15853</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>109.01</v>
+        <v>112.23</v>
       </c>
       <c r="B308" t="n">
-        <v>34531</v>
+        <v>24538</v>
       </c>
       <c r="C308" t="n">
-        <v>110.92</v>
+        <v>113.39</v>
       </c>
       <c r="D308" t="n">
-        <v>14726</v>
+        <v>24406</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>107.27</v>
+        <v>112.38</v>
       </c>
       <c r="B309" t="n">
-        <v>38525</v>
+        <v>23345</v>
       </c>
       <c r="C309" t="n">
-        <v>103.58</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="D309" t="n">
-        <v>11296</v>
+        <v>20982</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>107.19</v>
+        <v>113.19</v>
       </c>
       <c r="B310" t="n">
-        <v>39017</v>
+        <v>22564</v>
       </c>
       <c r="C310" t="n">
-        <v>103.7</v>
+        <v>98.88</v>
       </c>
       <c r="D310" t="n">
-        <v>22787</v>
+        <v>19140</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>127.97</v>
+        <v>113.65</v>
       </c>
       <c r="B311" t="n">
-        <v>21726</v>
+        <v>21430</v>
       </c>
       <c r="C311" t="n">
-        <v>133.61</v>
+        <v>101.33</v>
       </c>
       <c r="D311" t="n">
-        <v>28616</v>
+        <v>13877</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>9.220000000000001</v>
+        <v>113.79</v>
       </c>
       <c r="B312" t="n">
-        <v>22244</v>
+        <v>21031</v>
       </c>
       <c r="C312" t="n">
-        <v>9.91</v>
+        <v>103.83</v>
       </c>
       <c r="D312" t="n">
-        <v>16916</v>
+        <v>15369</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>98.56</v>
+        <v>114.05</v>
       </c>
       <c r="B313" t="n">
-        <v>44264</v>
+        <v>20630</v>
       </c>
       <c r="C313" t="n">
-        <v>100.31</v>
+        <v>132.77</v>
       </c>
       <c r="D313" t="n">
-        <v>25609</v>
+        <v>21111</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>98.28</v>
+        <v>114.28</v>
       </c>
       <c r="B314" t="n">
-        <v>42305</v>
+        <v>22097</v>
       </c>
       <c r="C314" t="n">
-        <v>101.64</v>
+        <v>133.75</v>
       </c>
       <c r="D314" t="n">
-        <v>22514</v>
+        <v>19735</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>95.39</v>
+        <v>114.74</v>
       </c>
       <c r="B315" t="n">
-        <v>37310</v>
+        <v>21619</v>
       </c>
       <c r="C315" t="n">
-        <v>98.08</v>
+        <v>117.83</v>
       </c>
       <c r="D315" t="n">
-        <v>27950</v>
+        <v>12402</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>107.58</v>
+        <v>114.87</v>
       </c>
       <c r="B316" t="n">
-        <v>40591</v>
+        <v>21416</v>
       </c>
       <c r="C316" t="n">
-        <v>106.71</v>
+        <v>117.98</v>
       </c>
       <c r="D316" t="n">
-        <v>20265</v>
+        <v>20496</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>92.64</v>
+        <v>115.01</v>
       </c>
       <c r="B317" t="n">
-        <v>26475</v>
+        <v>20091</v>
       </c>
       <c r="C317" t="n">
-        <v>94.13</v>
+        <v>132.59</v>
       </c>
       <c r="D317" t="n">
-        <v>18736</v>
+        <v>10308</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>103.77</v>
+        <v>115.69</v>
       </c>
       <c r="B318" t="n">
-        <v>47054</v>
+        <v>19750</v>
       </c>
       <c r="C318" t="n">
-        <v>107.64</v>
+        <v>116.65</v>
       </c>
       <c r="D318" t="n">
-        <v>23085</v>
+        <v>23761</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>92.08</v>
+        <v>115.72</v>
       </c>
       <c r="B319" t="n">
-        <v>27943</v>
+        <v>19627</v>
       </c>
       <c r="C319" t="n">
-        <v>90.39</v>
+        <v>118.51</v>
       </c>
       <c r="D319" t="n">
-        <v>21502</v>
+        <v>23298</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>101.23</v>
+        <v>115.84</v>
       </c>
       <c r="B320" t="n">
-        <v>43577</v>
+        <v>19918</v>
       </c>
       <c r="C320" t="n">
-        <v>101.69</v>
+        <v>132.31</v>
       </c>
       <c r="D320" t="n">
-        <v>19554</v>
+        <v>11174</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>100.8</v>
+        <v>116.06</v>
       </c>
       <c r="B321" t="n">
-        <v>44716</v>
+        <v>19602</v>
       </c>
       <c r="C321" t="n">
-        <v>102.23</v>
+        <v>125.71</v>
       </c>
       <c r="D321" t="n">
-        <v>28729</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>96.31999999999999</v>
+        <v>116.1</v>
       </c>
       <c r="B322" t="n">
-        <v>35991</v>
+        <v>19495</v>
       </c>
       <c r="C322" t="n">
-        <v>98.61</v>
+        <v>110.83</v>
       </c>
       <c r="D322" t="n">
-        <v>12464</v>
+        <v>26921</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>43.57</v>
+        <v>116.24</v>
       </c>
       <c r="B323" t="n">
-        <v>25223</v>
+        <v>20856</v>
       </c>
       <c r="C323" t="n">
-        <v>44.79</v>
+        <v>115.37</v>
       </c>
       <c r="D323" t="n">
-        <v>27904</v>
+        <v>24477</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>13.17</v>
+        <v>116.31</v>
       </c>
       <c r="B324" t="n">
-        <v>23184</v>
+        <v>18707</v>
       </c>
       <c r="C324" t="n">
-        <v>13.5</v>
+        <v>112.76</v>
       </c>
       <c r="D324" t="n">
-        <v>10920</v>
+        <v>28832</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>93.61</v>
+        <v>116.43</v>
       </c>
       <c r="B325" t="n">
-        <v>29950</v>
+        <v>20650</v>
       </c>
       <c r="C325" t="n">
-        <v>92.06999999999999</v>
+        <v>118.56</v>
       </c>
       <c r="D325" t="n">
-        <v>20097</v>
+        <v>20498</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>131.43</v>
+        <v>116.48</v>
       </c>
       <c r="B326" t="n">
-        <v>21772</v>
+        <v>19853</v>
       </c>
       <c r="C326" t="n">
-        <v>135.19</v>
+        <v>97.87</v>
       </c>
       <c r="D326" t="n">
-        <v>21578</v>
+        <v>20521</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>92.70999999999999</v>
+        <v>116.56</v>
       </c>
       <c r="B327" t="n">
-        <v>28440</v>
+        <v>21011</v>
       </c>
       <c r="C327" t="n">
-        <v>94.69</v>
+        <v>137.01</v>
       </c>
       <c r="D327" t="n">
-        <v>24923</v>
+        <v>27483</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>101.36</v>
+        <v>116.99</v>
       </c>
       <c r="B328" t="n">
-        <v>42919</v>
+        <v>18254</v>
       </c>
       <c r="C328" t="n">
-        <v>99.91</v>
+        <v>125.07</v>
       </c>
       <c r="D328" t="n">
-        <v>20753</v>
+        <v>16671</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>103.2</v>
+        <v>117.35</v>
       </c>
       <c r="B329" t="n">
-        <v>46987</v>
+        <v>21355</v>
       </c>
       <c r="C329" t="n">
-        <v>103.82</v>
+        <v>122.08</v>
       </c>
       <c r="D329" t="n">
-        <v>27139</v>
+        <v>29257</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>107.33</v>
+        <v>117.36</v>
       </c>
       <c r="B330" t="n">
-        <v>42885</v>
+        <v>19613</v>
       </c>
       <c r="C330" t="n">
-        <v>106.76</v>
+        <v>109.7</v>
       </c>
       <c r="D330" t="n">
-        <v>28390</v>
+        <v>19493</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>102.19</v>
+        <v>117.44</v>
       </c>
       <c r="B331" t="n">
-        <v>47213</v>
+        <v>21309</v>
       </c>
       <c r="C331" t="n">
-        <v>105.36</v>
+        <v>112.13</v>
       </c>
       <c r="D331" t="n">
-        <v>23052</v>
+        <v>26989</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>177.61</v>
+        <v>117.8</v>
       </c>
       <c r="B332" t="n">
-        <v>23404</v>
+        <v>20586</v>
       </c>
       <c r="C332" t="n">
-        <v>177.13</v>
+        <v>132.58</v>
       </c>
       <c r="D332" t="n">
-        <v>13781</v>
+        <v>27818</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>97.61</v>
+        <v>117.84</v>
       </c>
       <c r="B333" t="n">
-        <v>39532</v>
+        <v>20586</v>
       </c>
       <c r="C333" t="n">
-        <v>96.2</v>
+        <v>98.19</v>
       </c>
       <c r="D333" t="n">
-        <v>14048</v>
+        <v>14705</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>92.98</v>
+        <v>117.86</v>
       </c>
       <c r="B334" t="n">
-        <v>27544</v>
+        <v>20755</v>
       </c>
       <c r="C334" t="n">
-        <v>91.43000000000001</v>
+        <v>120.09</v>
       </c>
       <c r="D334" t="n">
-        <v>11073</v>
+        <v>28879</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>114.14</v>
+        <v>118.14</v>
       </c>
       <c r="B335" t="n">
-        <v>23571</v>
+        <v>19236</v>
       </c>
       <c r="C335" t="n">
-        <v>114.74</v>
+        <v>105.62</v>
       </c>
       <c r="D335" t="n">
-        <v>13404</v>
+        <v>28496</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>111.48</v>
+        <v>118.38</v>
       </c>
       <c r="B336" t="n">
-        <v>28887</v>
+        <v>19133</v>
       </c>
       <c r="C336" t="n">
-        <v>113.23</v>
+        <v>119.64</v>
       </c>
       <c r="D336" t="n">
-        <v>17390</v>
+        <v>24214</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>0.67</v>
+        <v>118.72</v>
       </c>
       <c r="B337" t="n">
-        <v>21841</v>
+        <v>18115</v>
       </c>
       <c r="C337" t="n">
-        <v>1.17</v>
+        <v>96.66</v>
       </c>
       <c r="D337" t="n">
-        <v>10443</v>
+        <v>13709</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>109.34</v>
+        <v>118.83</v>
       </c>
       <c r="B338" t="n">
-        <v>33815</v>
+        <v>19228</v>
       </c>
       <c r="C338" t="n">
-        <v>111.91</v>
+        <v>120.56</v>
       </c>
       <c r="D338" t="n">
-        <v>27890</v>
+        <v>14036</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>112.81</v>
+        <v>120.2</v>
       </c>
       <c r="B339" t="n">
-        <v>27492</v>
+        <v>18493</v>
       </c>
       <c r="C339" t="n">
-        <v>112.13</v>
+        <v>130.78</v>
       </c>
       <c r="D339" t="n">
-        <v>24267</v>
+        <v>24570</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>102.25</v>
+        <v>120.51</v>
       </c>
       <c r="B340" t="n">
-        <v>45627</v>
+        <v>17864</v>
       </c>
       <c r="C340" t="n">
-        <v>102.34</v>
+        <v>108.49</v>
       </c>
       <c r="D340" t="n">
-        <v>11482</v>
+        <v>12262</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>94.83</v>
+        <v>120.81</v>
       </c>
       <c r="B341" t="n">
-        <v>32796</v>
+        <v>19728</v>
       </c>
       <c r="C341" t="n">
-        <v>95.43000000000001</v>
+        <v>128.3</v>
       </c>
       <c r="D341" t="n">
-        <v>13424</v>
+        <v>20169</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>92.26000000000001</v>
+        <v>120.99</v>
       </c>
       <c r="B342" t="n">
-        <v>28478</v>
+        <v>19143</v>
       </c>
       <c r="C342" t="n">
-        <v>91.09999999999999</v>
+        <v>123.13</v>
       </c>
       <c r="D342" t="n">
-        <v>20535</v>
+        <v>24414</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>99.42</v>
+        <v>122.66</v>
       </c>
       <c r="B343" t="n">
-        <v>47412</v>
+        <v>19686</v>
       </c>
       <c r="C343" t="n">
-        <v>96.56999999999999</v>
+        <v>135.09</v>
       </c>
       <c r="D343" t="n">
-        <v>11077</v>
+        <v>25943</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>93.84</v>
+        <v>122.9</v>
       </c>
       <c r="B344" t="n">
-        <v>30200</v>
+        <v>19281</v>
       </c>
       <c r="C344" t="n">
-        <v>96.02</v>
+        <v>102.45</v>
       </c>
       <c r="D344" t="n">
-        <v>13058</v>
+        <v>21548</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>113.66</v>
+        <v>123.35</v>
       </c>
       <c r="B345" t="n">
-        <v>25179</v>
+        <v>19606</v>
       </c>
       <c r="C345" t="n">
-        <v>114.4</v>
+        <v>134.35</v>
       </c>
       <c r="D345" t="n">
-        <v>18997</v>
+        <v>24407</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>91.78</v>
+        <v>123.5</v>
       </c>
       <c r="B346" t="n">
-        <v>24362</v>
+        <v>21286</v>
       </c>
       <c r="C346" t="n">
-        <v>93.02</v>
+        <v>122.13</v>
       </c>
       <c r="D346" t="n">
-        <v>15084</v>
+        <v>19572</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>104.86</v>
+        <v>124.26</v>
       </c>
       <c r="B347" t="n">
-        <v>47504</v>
+        <v>18342</v>
       </c>
       <c r="C347" t="n">
-        <v>108.31</v>
+        <v>113.9</v>
       </c>
       <c r="D347" t="n">
-        <v>19954</v>
+        <v>26602</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>109.33</v>
+        <v>124.56</v>
       </c>
       <c r="B348" t="n">
-        <v>35437</v>
+        <v>18648</v>
       </c>
       <c r="C348" t="n">
-        <v>111.4</v>
+        <v>94.2</v>
       </c>
       <c r="D348" t="n">
-        <v>12200</v>
+        <v>11612</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>113.22</v>
+        <v>124.61</v>
       </c>
       <c r="B349" t="n">
-        <v>23361</v>
+        <v>18227</v>
       </c>
       <c r="C349" t="n">
-        <v>111.96</v>
+        <v>137.42</v>
       </c>
       <c r="D349" t="n">
-        <v>10016</v>
+        <v>15570</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>90.39</v>
+        <v>124.81</v>
       </c>
       <c r="B350" t="n">
-        <v>22899</v>
+        <v>19430</v>
       </c>
       <c r="C350" t="n">
-        <v>90.93000000000001</v>
+        <v>111.43</v>
       </c>
       <c r="D350" t="n">
-        <v>10192</v>
+        <v>17650</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>95.45999999999999</v>
+        <v>125.05</v>
       </c>
       <c r="B351" t="n">
-        <v>36889</v>
+        <v>19392</v>
       </c>
       <c r="C351" t="n">
-        <v>94.31999999999999</v>
+        <v>140.82</v>
       </c>
       <c r="D351" t="n">
-        <v>13505</v>
+        <v>22821</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>106.1</v>
+        <v>125.81</v>
       </c>
       <c r="B352" t="n">
-        <v>42797</v>
+        <v>18581</v>
       </c>
       <c r="C352" t="n">
-        <v>104.82</v>
+        <v>114.44</v>
       </c>
       <c r="D352" t="n">
-        <v>23221</v>
+        <v>29296</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>102.05</v>
+        <v>125.84</v>
       </c>
       <c r="B353" t="n">
-        <v>46913</v>
+        <v>18028</v>
       </c>
       <c r="C353" t="n">
-        <v>103.49</v>
+        <v>150.16</v>
       </c>
       <c r="D353" t="n">
-        <v>24450</v>
+        <v>20773</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>98.56</v>
+        <v>127.13</v>
       </c>
       <c r="B354" t="n">
-        <v>43235</v>
+        <v>19687</v>
       </c>
       <c r="C354" t="n">
-        <v>97.20999999999999</v>
+        <v>120.26</v>
       </c>
       <c r="D354" t="n">
-        <v>11757</v>
+        <v>17302</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>94.98999999999999</v>
+        <v>127.68</v>
       </c>
       <c r="B355" t="n">
-        <v>33600</v>
+        <v>19593</v>
       </c>
       <c r="C355" t="n">
-        <v>97.65000000000001</v>
+        <v>133.19</v>
       </c>
       <c r="D355" t="n">
-        <v>28779</v>
+        <v>21783</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>103.95</v>
+        <v>128.14</v>
       </c>
       <c r="B356" t="n">
-        <v>47330</v>
+        <v>19150</v>
       </c>
       <c r="C356" t="n">
-        <v>101.91</v>
+        <v>108.38</v>
       </c>
       <c r="D356" t="n">
-        <v>25407</v>
+        <v>29821</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>92.76000000000001</v>
+        <v>128.97</v>
       </c>
       <c r="B357" t="n">
-        <v>28843</v>
+        <v>19730</v>
       </c>
       <c r="C357" t="n">
-        <v>95.17</v>
+        <v>123.52</v>
       </c>
       <c r="D357" t="n">
-        <v>19759</v>
+        <v>25556</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>106.42</v>
+        <v>129.08</v>
       </c>
       <c r="B358" t="n">
-        <v>41545</v>
+        <v>21704</v>
       </c>
       <c r="C358" t="n">
-        <v>109.67</v>
+        <v>146.96</v>
       </c>
       <c r="D358" t="n">
-        <v>16355</v>
+        <v>25399</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>102.58</v>
+        <v>129.43</v>
       </c>
       <c r="B359" t="n">
-        <v>46593</v>
+        <v>19298</v>
       </c>
       <c r="C359" t="n">
-        <v>103.55</v>
+        <v>147.69</v>
       </c>
       <c r="D359" t="n">
-        <v>16650</v>
+        <v>20568</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>102.94</v>
+        <v>129.52</v>
       </c>
       <c r="B360" t="n">
-        <v>45236</v>
+        <v>20306</v>
       </c>
       <c r="C360" t="n">
-        <v>104.34</v>
+        <v>107.78</v>
       </c>
       <c r="D360" t="n">
-        <v>14456</v>
+        <v>14220</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>101.95</v>
+        <v>129.96</v>
       </c>
       <c r="B361" t="n">
-        <v>46022</v>
+        <v>19626</v>
       </c>
       <c r="C361" t="n">
-        <v>100.17</v>
+        <v>108.86</v>
       </c>
       <c r="D361" t="n">
-        <v>26343</v>
+        <v>27347</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>98.56999999999999</v>
+        <v>129.97</v>
       </c>
       <c r="B362" t="n">
-        <v>42737</v>
+        <v>19225</v>
       </c>
       <c r="C362" t="n">
-        <v>99.06</v>
+        <v>139.02</v>
       </c>
       <c r="D362" t="n">
-        <v>26802</v>
+        <v>23081</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>112.22</v>
+        <v>130.21</v>
       </c>
       <c r="B363" t="n">
-        <v>26257</v>
+        <v>19137</v>
       </c>
       <c r="C363" t="n">
-        <v>114.87</v>
+        <v>117.84</v>
       </c>
       <c r="D363" t="n">
-        <v>14707</v>
+        <v>27637</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>91.90000000000001</v>
+        <v>130.92</v>
       </c>
       <c r="B364" t="n">
-        <v>25839</v>
+        <v>19473</v>
       </c>
       <c r="C364" t="n">
-        <v>89.73999999999999</v>
+        <v>114.4</v>
       </c>
       <c r="D364" t="n">
-        <v>18851</v>
+        <v>27018</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>100.93</v>
+        <v>130.99</v>
       </c>
       <c r="B365" t="n">
-        <v>44423</v>
+        <v>21442</v>
       </c>
       <c r="C365" t="n">
-        <v>102.32</v>
+        <v>144.09</v>
       </c>
       <c r="D365" t="n">
-        <v>11694</v>
+        <v>24821</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>109.43</v>
+        <v>131.16</v>
       </c>
       <c r="B366" t="n">
-        <v>30936</v>
+        <v>21452</v>
       </c>
       <c r="C366" t="n">
-        <v>105.47</v>
+        <v>124.16</v>
       </c>
       <c r="D366" t="n">
-        <v>14778</v>
+        <v>11286</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>13.69</v>
+        <v>131.57</v>
       </c>
       <c r="B367" t="n">
-        <v>27260</v>
+        <v>21802</v>
       </c>
       <c r="C367" t="n">
-        <v>13.56</v>
+        <v>110.42</v>
       </c>
       <c r="D367" t="n">
-        <v>27959</v>
+        <v>27583</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>106.63</v>
+        <v>131.74</v>
       </c>
       <c r="B368" t="n">
-        <v>44083</v>
+        <v>20332</v>
       </c>
       <c r="C368" t="n">
-        <v>106.83</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D368" t="n">
-        <v>14011</v>
+        <v>24806</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>101.76</v>
+        <v>131.8</v>
       </c>
       <c r="B369" t="n">
-        <v>46342</v>
+        <v>20704</v>
       </c>
       <c r="C369" t="n">
-        <v>100.15</v>
+        <v>115.39</v>
       </c>
       <c r="D369" t="n">
-        <v>22559</v>
+        <v>10793</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>107.86</v>
+        <v>133.06</v>
       </c>
       <c r="B370" t="n">
-        <v>37914</v>
+        <v>18447</v>
       </c>
       <c r="C370" t="n">
-        <v>107.81</v>
+        <v>150.16</v>
       </c>
       <c r="D370" t="n">
-        <v>15762</v>
+        <v>23176</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>108.61</v>
+        <v>133.16</v>
       </c>
       <c r="B371" t="n">
-        <v>36672</v>
+        <v>18706</v>
       </c>
       <c r="C371" t="n">
-        <v>109.7</v>
+        <v>119.31</v>
       </c>
       <c r="D371" t="n">
-        <v>11151</v>
+        <v>10817</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>100.23</v>
+        <v>133.17</v>
       </c>
       <c r="B372" t="n">
-        <v>44590</v>
+        <v>18205</v>
       </c>
       <c r="C372" t="n">
-        <v>103.11</v>
+        <v>140.73</v>
       </c>
       <c r="D372" t="n">
-        <v>26532</v>
+        <v>11956</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>94.62</v>
+        <v>133.3</v>
       </c>
       <c r="B373" t="n">
-        <v>30177</v>
+        <v>19366</v>
       </c>
       <c r="C373" t="n">
-        <v>93.86</v>
+        <v>153.3</v>
       </c>
       <c r="D373" t="n">
-        <v>15249</v>
+        <v>14708</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>105.3</v>
+        <v>133.45</v>
       </c>
       <c r="B374" t="n">
-        <v>46155</v>
+        <v>19955</v>
       </c>
       <c r="C374" t="n">
-        <v>104.95</v>
+        <v>127.43</v>
       </c>
       <c r="D374" t="n">
-        <v>25414</v>
+        <v>27212</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>112.86</v>
+        <v>133.72</v>
       </c>
       <c r="B375" t="n">
-        <v>25189</v>
+        <v>19159</v>
       </c>
       <c r="C375" t="n">
-        <v>110.47</v>
+        <v>133.46</v>
       </c>
       <c r="D375" t="n">
-        <v>14804</v>
+        <v>16809</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>96.86</v>
+        <v>133.9</v>
       </c>
       <c r="B376" t="n">
-        <v>37328</v>
+        <v>16964</v>
       </c>
       <c r="C376" t="n">
-        <v>97.36</v>
+        <v>114.19</v>
       </c>
       <c r="D376" t="n">
-        <v>13681</v>
+        <v>22347</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>106.1</v>
+        <v>134.27</v>
       </c>
       <c r="B377" t="n">
-        <v>43050</v>
+        <v>20745</v>
       </c>
       <c r="C377" t="n">
-        <v>104.59</v>
+        <v>120.5</v>
       </c>
       <c r="D377" t="n">
-        <v>16145</v>
+        <v>10901</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>112.47</v>
+        <v>134.33</v>
       </c>
       <c r="B378" t="n">
-        <v>23154</v>
+        <v>18989</v>
       </c>
       <c r="C378" t="n">
-        <v>109.68</v>
+        <v>147.03</v>
       </c>
       <c r="D378" t="n">
-        <v>27712</v>
+        <v>24531</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>52.77</v>
+        <v>134.35</v>
       </c>
       <c r="B379" t="n">
-        <v>20955</v>
+        <v>19439</v>
       </c>
       <c r="C379" t="n">
-        <v>52.07</v>
+        <v>114.66</v>
       </c>
       <c r="D379" t="n">
-        <v>23720</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>108.17</v>
+        <v>135.5</v>
       </c>
       <c r="B380" t="n">
-        <v>37080</v>
+        <v>16448</v>
       </c>
       <c r="C380" t="n">
-        <v>106.19</v>
+        <v>159.68</v>
       </c>
       <c r="D380" t="n">
-        <v>13276</v>
+        <v>20792</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>104.38</v>
+        <v>135.63</v>
       </c>
       <c r="B381" t="n">
-        <v>44906</v>
+        <v>20649</v>
       </c>
       <c r="C381" t="n">
-        <v>108</v>
+        <v>157.45</v>
       </c>
       <c r="D381" t="n">
-        <v>14366</v>
+        <v>23964</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>108.51</v>
+        <v>136.73</v>
       </c>
       <c r="B382" t="n">
-        <v>34657</v>
+        <v>17647</v>
       </c>
       <c r="C382" t="n">
-        <v>108.79</v>
+        <v>155.61</v>
       </c>
       <c r="D382" t="n">
-        <v>10925</v>
+        <v>18409</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>100.33</v>
+        <v>137.8</v>
       </c>
       <c r="B383" t="n">
-        <v>46072</v>
+        <v>17603</v>
       </c>
       <c r="C383" t="n">
-        <v>97.16</v>
+        <v>148.09</v>
       </c>
       <c r="D383" t="n">
-        <v>13424</v>
+        <v>25604</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>102.21</v>
+        <v>138.07</v>
       </c>
       <c r="B384" t="n">
-        <v>45417</v>
+        <v>18687</v>
       </c>
       <c r="C384" t="n">
-        <v>100.98</v>
+        <v>164.42</v>
       </c>
       <c r="D384" t="n">
-        <v>23532</v>
+        <v>19836</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>102.78</v>
+        <v>138.49</v>
       </c>
       <c r="B385" t="n">
-        <v>43378</v>
+        <v>18975</v>
       </c>
       <c r="C385" t="n">
-        <v>103.13</v>
+        <v>151.16</v>
       </c>
       <c r="D385" t="n">
-        <v>11646</v>
+        <v>15060</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>116.95</v>
+        <v>138.56</v>
       </c>
       <c r="B386" t="n">
-        <v>28442</v>
+        <v>22001</v>
       </c>
       <c r="C386" t="n">
-        <v>117.51</v>
+        <v>124.02</v>
       </c>
       <c r="D386" t="n">
-        <v>17176</v>
+        <v>22569</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>103.04</v>
+        <v>138.94</v>
       </c>
       <c r="B387" t="n">
-        <v>47520</v>
+        <v>18742</v>
       </c>
       <c r="C387" t="n">
-        <v>105.17</v>
+        <v>120.89</v>
       </c>
       <c r="D387" t="n">
-        <v>12839</v>
+        <v>13939</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>96.18000000000001</v>
+        <v>139.14</v>
       </c>
       <c r="B388" t="n">
-        <v>37341</v>
+        <v>17728</v>
       </c>
       <c r="C388" t="n">
-        <v>97.95999999999999</v>
+        <v>143.7</v>
       </c>
       <c r="D388" t="n">
-        <v>20937</v>
+        <v>16985</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>104.71</v>
+        <v>139.48</v>
       </c>
       <c r="B389" t="n">
-        <v>45488</v>
+        <v>15560</v>
       </c>
       <c r="C389" t="n">
-        <v>104.94</v>
+        <v>122.82</v>
       </c>
       <c r="D389" t="n">
-        <v>27771</v>
+        <v>10435</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>109.93</v>
+        <v>139.6</v>
       </c>
       <c r="B390" t="n">
-        <v>32516</v>
+        <v>16671</v>
       </c>
       <c r="C390" t="n">
-        <v>106.57</v>
+        <v>132.59</v>
       </c>
       <c r="D390" t="n">
-        <v>10598</v>
+        <v>13469</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>92.94</v>
+        <v>139.83</v>
       </c>
       <c r="B391" t="n">
-        <v>30576</v>
+        <v>21803</v>
       </c>
       <c r="C391" t="n">
-        <v>92.92</v>
+        <v>117.06</v>
       </c>
       <c r="D391" t="n">
-        <v>24162</v>
+        <v>29412</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>112.1</v>
+        <v>139.98</v>
       </c>
       <c r="B392" t="n">
-        <v>27076</v>
+        <v>16777</v>
       </c>
       <c r="C392" t="n">
-        <v>108.93</v>
+        <v>157.16</v>
       </c>
       <c r="D392" t="n">
-        <v>17284</v>
+        <v>13331</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>146.46</v>
+        <v>141.78</v>
       </c>
       <c r="B393" t="n">
-        <v>23109</v>
+        <v>18381</v>
       </c>
       <c r="C393" t="n">
-        <v>146.2</v>
+        <v>130.27</v>
       </c>
       <c r="D393" t="n">
-        <v>14189</v>
+        <v>13421</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>38.54</v>
+        <v>142.24</v>
       </c>
       <c r="B394" t="n">
-        <v>26993</v>
+        <v>20429</v>
       </c>
       <c r="C394" t="n">
-        <v>37.89</v>
+        <v>135.32</v>
       </c>
       <c r="D394" t="n">
-        <v>19543</v>
+        <v>23927</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>70.27</v>
+        <v>142.41</v>
       </c>
       <c r="B395" t="n">
-        <v>22632</v>
+        <v>18161</v>
       </c>
       <c r="C395" t="n">
-        <v>67.84</v>
+        <v>153.14</v>
       </c>
       <c r="D395" t="n">
-        <v>23430</v>
+        <v>10471</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>109.81</v>
+        <v>143.61</v>
       </c>
       <c r="B396" t="n">
-        <v>33226</v>
+        <v>19064</v>
       </c>
       <c r="C396" t="n">
-        <v>111.03</v>
+        <v>161.83</v>
       </c>
       <c r="D396" t="n">
-        <v>17556</v>
+        <v>14406</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>108.33</v>
+        <v>144.43</v>
       </c>
       <c r="B397" t="n">
-        <v>40549</v>
+        <v>20875</v>
       </c>
       <c r="C397" t="n">
-        <v>112.01</v>
+        <v>115.04</v>
       </c>
       <c r="D397" t="n">
-        <v>23660</v>
+        <v>13852</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>113.63</v>
+        <v>144.46</v>
       </c>
       <c r="B398" t="n">
-        <v>27072</v>
+        <v>18672</v>
       </c>
       <c r="C398" t="n">
-        <v>113.56</v>
+        <v>120.17</v>
       </c>
       <c r="D398" t="n">
-        <v>14425</v>
+        <v>19845</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>117.76</v>
+        <v>145.18</v>
       </c>
       <c r="B399" t="n">
-        <v>22714</v>
+        <v>17013</v>
       </c>
       <c r="C399" t="n">
-        <v>115.63</v>
+        <v>131.16</v>
       </c>
       <c r="D399" t="n">
-        <v>26596</v>
+        <v>11744</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>92.22</v>
+        <v>145.59</v>
       </c>
       <c r="B400" t="n">
-        <v>27725</v>
+        <v>20042</v>
       </c>
       <c r="C400" t="n">
-        <v>93.23999999999999</v>
+        <v>150.3</v>
       </c>
       <c r="D400" t="n">
-        <v>16793</v>
+        <v>28654</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>101.05</v>
+        <v>145.84</v>
       </c>
       <c r="B401" t="n">
-        <v>47234</v>
+        <v>19998</v>
       </c>
       <c r="C401" t="n">
-        <v>101.19</v>
+        <v>136.11</v>
       </c>
       <c r="D401" t="n">
-        <v>28701</v>
+        <v>23854</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>114.53</v>
+        <v>146.93</v>
       </c>
       <c r="B402" t="n">
-        <v>22238</v>
+        <v>22090</v>
       </c>
       <c r="C402" t="n">
-        <v>114.41</v>
+        <v>172.76</v>
       </c>
       <c r="D402" t="n">
-        <v>23895</v>
+        <v>23692</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>100.89</v>
+        <v>148.36</v>
       </c>
       <c r="B403" t="n">
-        <v>43893</v>
+        <v>21298</v>
       </c>
       <c r="C403" t="n">
-        <v>100.88</v>
+        <v>155.53</v>
       </c>
       <c r="D403" t="n">
-        <v>29703</v>
+        <v>15731</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>95.61</v>
+        <v>148.72</v>
       </c>
       <c r="B404" t="n">
-        <v>36540</v>
+        <v>22252</v>
       </c>
       <c r="C404" t="n">
-        <v>98.81999999999999</v>
+        <v>144.36</v>
       </c>
       <c r="D404" t="n">
-        <v>18477</v>
+        <v>13062</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>103.52</v>
+        <v>148.79</v>
       </c>
       <c r="B405" t="n">
-        <v>48342</v>
+        <v>21987</v>
       </c>
       <c r="C405" t="n">
-        <v>103.65</v>
+        <v>131.78</v>
       </c>
       <c r="D405" t="n">
-        <v>21396</v>
+        <v>27878</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>94.45</v>
+        <v>149.87</v>
       </c>
       <c r="B406" t="n">
-        <v>31997</v>
+        <v>25240</v>
       </c>
       <c r="C406" t="n">
-        <v>94.68000000000001</v>
+        <v>171.56</v>
       </c>
       <c r="D406" t="n">
-        <v>15460</v>
+        <v>15162</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>75.55</v>
+        <v>149.87</v>
       </c>
       <c r="B407" t="n">
-        <v>25160</v>
+        <v>24846</v>
       </c>
       <c r="C407" t="n">
-        <v>72.61</v>
+        <v>156.19</v>
       </c>
       <c r="D407" t="n">
-        <v>14791</v>
+        <v>19282</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>111.32</v>
+        <v>149.94</v>
       </c>
       <c r="B408" t="n">
-        <v>25904</v>
+        <v>20445</v>
       </c>
       <c r="C408" t="n">
-        <v>111.88</v>
+        <v>136.87</v>
       </c>
       <c r="D408" t="n">
-        <v>11526</v>
+        <v>29140</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>103.77</v>
+        <v>150.19</v>
       </c>
       <c r="B409" t="n">
-        <v>45792</v>
+        <v>25405</v>
       </c>
       <c r="C409" t="n">
-        <v>101.69</v>
+        <v>134.66</v>
       </c>
       <c r="D409" t="n">
-        <v>22113</v>
+        <v>13602</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>45.31</v>
+        <v>150.6</v>
       </c>
       <c r="B410" t="n">
-        <v>23903</v>
+        <v>23906</v>
       </c>
       <c r="C410" t="n">
-        <v>44.88</v>
+        <v>173.52</v>
       </c>
       <c r="D410" t="n">
-        <v>14079</v>
+        <v>27673</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>20.75</v>
+        <v>150.63</v>
       </c>
       <c r="B411" t="n">
-        <v>24121</v>
+        <v>25296</v>
       </c>
       <c r="C411" t="n">
-        <v>22.26</v>
+        <v>127.39</v>
       </c>
       <c r="D411" t="n">
-        <v>15833</v>
+        <v>27726</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>43.84</v>
+        <v>150.65</v>
       </c>
       <c r="B412" t="n">
-        <v>24009</v>
+        <v>25938</v>
       </c>
       <c r="C412" t="n">
-        <v>44.55</v>
+        <v>178.01</v>
       </c>
       <c r="D412" t="n">
-        <v>21407</v>
+        <v>17167</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>92.68000000000001</v>
+        <v>150.95</v>
       </c>
       <c r="B413" t="n">
-        <v>26163</v>
+        <v>26014</v>
       </c>
       <c r="C413" t="n">
-        <v>91.88</v>
+        <v>134.44</v>
       </c>
       <c r="D413" t="n">
-        <v>18241</v>
+        <v>14726</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>90.56999999999999</v>
+        <v>151.74</v>
       </c>
       <c r="B414" t="n">
-        <v>24514</v>
+        <v>24478</v>
       </c>
       <c r="C414" t="n">
-        <v>94.38</v>
+        <v>164.74</v>
       </c>
       <c r="D414" t="n">
-        <v>19299</v>
+        <v>22934</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>113.86</v>
+        <v>151.88</v>
       </c>
       <c r="B415" t="n">
-        <v>22268</v>
+        <v>27137</v>
       </c>
       <c r="C415" t="n">
-        <v>112.28</v>
+        <v>178.12</v>
       </c>
       <c r="D415" t="n">
-        <v>17515</v>
+        <v>21761</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>174.58</v>
+        <v>152.21</v>
       </c>
       <c r="B416" t="n">
-        <v>23319</v>
+        <v>25483</v>
       </c>
       <c r="C416" t="n">
-        <v>179.12</v>
+        <v>124.64</v>
       </c>
       <c r="D416" t="n">
-        <v>28111</v>
+        <v>20772</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>131.09</v>
+        <v>152.24</v>
       </c>
       <c r="B417" t="n">
-        <v>22730</v>
+        <v>24853</v>
       </c>
       <c r="C417" t="n">
-        <v>128.72</v>
+        <v>151.1</v>
       </c>
       <c r="D417" t="n">
-        <v>21902</v>
+        <v>11982</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>102.98</v>
+        <v>152.48</v>
       </c>
       <c r="B418" t="n">
-        <v>46287</v>
+        <v>24770</v>
       </c>
       <c r="C418" t="n">
-        <v>99.64</v>
+        <v>123.83</v>
       </c>
       <c r="D418" t="n">
-        <v>20583</v>
+        <v>15555</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>101.53</v>
+        <v>152.56</v>
       </c>
       <c r="B419" t="n">
-        <v>45781</v>
+        <v>26550</v>
       </c>
       <c r="C419" t="n">
-        <v>100.09</v>
+        <v>149</v>
       </c>
       <c r="D419" t="n">
-        <v>17490</v>
+        <v>16821</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>111.21</v>
+        <v>153.02</v>
       </c>
       <c r="B420" t="n">
-        <v>30026</v>
+        <v>24367</v>
       </c>
       <c r="C420" t="n">
-        <v>110.06</v>
+        <v>176.59</v>
       </c>
       <c r="D420" t="n">
-        <v>23111</v>
+        <v>25048</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>93.04000000000001</v>
+        <v>154.46</v>
       </c>
       <c r="B421" t="n">
-        <v>29623</v>
+        <v>28213</v>
       </c>
       <c r="C421" t="n">
-        <v>95.2</v>
+        <v>180</v>
       </c>
       <c r="D421" t="n">
-        <v>29033</v>
+        <v>29018</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>105.23</v>
+        <v>154.86</v>
       </c>
       <c r="B422" t="n">
-        <v>44570</v>
+        <v>24618</v>
       </c>
       <c r="C422" t="n">
-        <v>106.73</v>
+        <v>170.29</v>
       </c>
       <c r="D422" t="n">
-        <v>23777</v>
+        <v>25540</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>93.77</v>
+        <v>154.93</v>
       </c>
       <c r="B423" t="n">
-        <v>28495</v>
+        <v>28151</v>
       </c>
       <c r="C423" t="n">
-        <v>95.52</v>
+        <v>136.65</v>
       </c>
       <c r="D423" t="n">
-        <v>14056</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>104.12</v>
+        <v>155.3</v>
       </c>
       <c r="B424" t="n">
-        <v>45768</v>
+        <v>29796</v>
       </c>
       <c r="C424" t="n">
-        <v>100.85</v>
+        <v>126.8</v>
       </c>
       <c r="D424" t="n">
-        <v>10567</v>
+        <v>29291</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>114.29</v>
+        <v>155.31</v>
       </c>
       <c r="B425" t="n">
-        <v>23210</v>
+        <v>27646</v>
       </c>
       <c r="C425" t="n">
-        <v>112.1</v>
+        <v>151.2</v>
       </c>
       <c r="D425" t="n">
-        <v>18369</v>
+        <v>10580</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>106.73</v>
+        <v>156.14</v>
       </c>
       <c r="B426" t="n">
-        <v>43344</v>
+        <v>28447</v>
       </c>
       <c r="C426" t="n">
-        <v>103.79</v>
+        <v>146.22</v>
       </c>
       <c r="D426" t="n">
-        <v>27295</v>
+        <v>19049</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>42.08</v>
+        <v>156.33</v>
       </c>
       <c r="B427" t="n">
-        <v>25000</v>
+        <v>28589</v>
       </c>
       <c r="C427" t="n">
-        <v>43.05</v>
+        <v>145.45</v>
       </c>
       <c r="D427" t="n">
-        <v>22879</v>
+        <v>25995</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>97.55</v>
+        <v>156.45</v>
       </c>
       <c r="B428" t="n">
-        <v>40130</v>
+        <v>31854</v>
       </c>
       <c r="C428" t="n">
-        <v>100.49</v>
+        <v>122.99</v>
       </c>
       <c r="D428" t="n">
-        <v>22149</v>
+        <v>16052</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>105.2</v>
+        <v>156.77</v>
       </c>
       <c r="B429" t="n">
-        <v>46058</v>
+        <v>29384</v>
       </c>
       <c r="C429" t="n">
-        <v>106.2</v>
+        <v>131.23</v>
       </c>
       <c r="D429" t="n">
-        <v>18237</v>
+        <v>13539</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>103.5</v>
+        <v>157.38</v>
       </c>
       <c r="B430" t="n">
-        <v>47508</v>
+        <v>30308</v>
       </c>
       <c r="C430" t="n">
-        <v>103.14</v>
+        <v>176.61</v>
       </c>
       <c r="D430" t="n">
-        <v>14676</v>
+        <v>28100</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>107.25</v>
+        <v>158.21</v>
       </c>
       <c r="B431" t="n">
-        <v>38341</v>
+        <v>30713</v>
       </c>
       <c r="C431" t="n">
-        <v>107.93</v>
+        <v>127.13</v>
       </c>
       <c r="D431" t="n">
-        <v>14220</v>
+        <v>26710</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>95.81</v>
+        <v>158.24</v>
       </c>
       <c r="B432" t="n">
-        <v>35187</v>
+        <v>30759</v>
       </c>
       <c r="C432" t="n">
-        <v>93.77</v>
+        <v>176.23</v>
       </c>
       <c r="D432" t="n">
-        <v>24490</v>
+        <v>15491</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>101.4</v>
+        <v>158.69</v>
       </c>
       <c r="B433" t="n">
-        <v>46939</v>
+        <v>31191</v>
       </c>
       <c r="C433" t="n">
-        <v>105.86</v>
+        <v>172.56</v>
       </c>
       <c r="D433" t="n">
-        <v>20256</v>
+        <v>24673</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>106.54</v>
+        <v>158.82</v>
       </c>
       <c r="B434" t="n">
-        <v>41345</v>
+        <v>32757</v>
       </c>
       <c r="C434" t="n">
-        <v>104.85</v>
+        <v>136.59</v>
       </c>
       <c r="D434" t="n">
-        <v>22991</v>
+        <v>27448</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>94.95999999999999</v>
+        <v>159.33</v>
       </c>
       <c r="B435" t="n">
-        <v>31985</v>
+        <v>30652</v>
       </c>
       <c r="C435" t="n">
-        <v>97.2</v>
+        <v>142.92</v>
       </c>
       <c r="D435" t="n">
-        <v>12126</v>
+        <v>18446</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>113.69</v>
+        <v>159.49</v>
       </c>
       <c r="B436" t="n">
-        <v>24126</v>
+        <v>30121</v>
       </c>
       <c r="C436" t="n">
-        <v>109.88</v>
+        <v>167.72</v>
       </c>
       <c r="D436" t="n">
-        <v>25127</v>
+        <v>26488</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>115.13</v>
+        <v>159.56</v>
       </c>
       <c r="B437" t="n">
-        <v>23679</v>
+        <v>31047</v>
       </c>
       <c r="C437" t="n">
-        <v>115.13</v>
+        <v>168.51</v>
       </c>
       <c r="D437" t="n">
-        <v>25795</v>
+        <v>24635</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>112.8</v>
+        <v>159.6</v>
       </c>
       <c r="B438" t="n">
-        <v>24785</v>
+        <v>32537</v>
       </c>
       <c r="C438" t="n">
-        <v>116.31</v>
+        <v>180</v>
       </c>
       <c r="D438" t="n">
-        <v>11333</v>
+        <v>12018</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>112.7</v>
+        <v>159.86</v>
       </c>
       <c r="B439" t="n">
-        <v>25944</v>
+        <v>31015</v>
       </c>
       <c r="C439" t="n">
-        <v>110.01</v>
+        <v>146.95</v>
       </c>
       <c r="D439" t="n">
-        <v>16035</v>
+        <v>15588</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>96.79000000000001</v>
+        <v>160.28</v>
       </c>
       <c r="B440" t="n">
-        <v>36942</v>
+        <v>30956</v>
       </c>
       <c r="C440" t="n">
-        <v>94.28</v>
+        <v>163.71</v>
       </c>
       <c r="D440" t="n">
-        <v>21203</v>
+        <v>29139</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>134.26</v>
+        <v>160.36</v>
       </c>
       <c r="B441" t="n">
-        <v>25310</v>
+        <v>31038</v>
       </c>
       <c r="C441" t="n">
-        <v>137.65</v>
+        <v>157.95</v>
       </c>
       <c r="D441" t="n">
-        <v>12635</v>
+        <v>18014</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>101.63</v>
+        <v>160.63</v>
       </c>
       <c r="B442" t="n">
-        <v>49434</v>
+        <v>31529</v>
       </c>
       <c r="C442" t="n">
-        <v>104.97</v>
+        <v>168.9</v>
       </c>
       <c r="D442" t="n">
-        <v>10383</v>
+        <v>15397</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>97.11</v>
+        <v>160.71</v>
       </c>
       <c r="B443" t="n">
-        <v>39318</v>
+        <v>29380</v>
       </c>
       <c r="C443" t="n">
-        <v>96.14</v>
+        <v>172.08</v>
       </c>
       <c r="D443" t="n">
-        <v>17950</v>
+        <v>20790</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>51.19</v>
+        <v>161.03</v>
       </c>
       <c r="B444" t="n">
-        <v>22196</v>
+        <v>30132</v>
       </c>
       <c r="C444" t="n">
-        <v>49.53</v>
+        <v>127.87</v>
       </c>
       <c r="D444" t="n">
-        <v>22418</v>
+        <v>28932</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>95.06</v>
+        <v>161.11</v>
       </c>
       <c r="B445" t="n">
-        <v>32045</v>
+        <v>30443</v>
       </c>
       <c r="C445" t="n">
-        <v>91.88</v>
+        <v>166.53</v>
       </c>
       <c r="D445" t="n">
-        <v>21416</v>
+        <v>11469</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>99.75</v>
+        <v>161.54</v>
       </c>
       <c r="B446" t="n">
-        <v>43226</v>
+        <v>31380</v>
       </c>
       <c r="C446" t="n">
-        <v>99.11</v>
+        <v>180</v>
       </c>
       <c r="D446" t="n">
-        <v>15930</v>
+        <v>22931</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>106.18</v>
+        <v>162.01</v>
       </c>
       <c r="B447" t="n">
-        <v>45097</v>
+        <v>30446</v>
       </c>
       <c r="C447" t="n">
-        <v>105.75</v>
+        <v>168.33</v>
       </c>
       <c r="D447" t="n">
-        <v>16629</v>
+        <v>22354</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>10.1</v>
+        <v>162.08</v>
       </c>
       <c r="B448" t="n">
-        <v>23832</v>
+        <v>31028</v>
       </c>
       <c r="C448" t="n">
-        <v>9.59</v>
+        <v>130.8</v>
       </c>
       <c r="D448" t="n">
-        <v>19119</v>
+        <v>12348</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>69.83</v>
+        <v>162.19</v>
       </c>
       <c r="B449" t="n">
-        <v>25845</v>
+        <v>29900</v>
       </c>
       <c r="C449" t="n">
-        <v>69.97</v>
+        <v>131.43</v>
       </c>
       <c r="D449" t="n">
-        <v>22981</v>
+        <v>17949</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>112.22</v>
+        <v>162.53</v>
       </c>
       <c r="B450" t="n">
-        <v>26667</v>
+        <v>31605</v>
       </c>
       <c r="C450" t="n">
-        <v>110.14</v>
+        <v>143.51</v>
       </c>
       <c r="D450" t="n">
-        <v>26513</v>
+        <v>10037</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>103.85</v>
+        <v>163.18</v>
       </c>
       <c r="B451" t="n">
-        <v>46562</v>
+        <v>29196</v>
       </c>
       <c r="C451" t="n">
-        <v>103.75</v>
+        <v>133.61</v>
       </c>
       <c r="D451" t="n">
-        <v>15092</v>
+        <v>14766</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>170.57</v>
+        <v>163.59</v>
       </c>
       <c r="B452" t="n">
-        <v>21010</v>
+        <v>30142</v>
       </c>
       <c r="C452" t="n">
-        <v>169.14</v>
+        <v>147.2</v>
       </c>
       <c r="D452" t="n">
-        <v>12765</v>
+        <v>16764</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>55.76</v>
+        <v>163.79</v>
       </c>
       <c r="B453" t="n">
-        <v>24325</v>
+        <v>29582</v>
       </c>
       <c r="C453" t="n">
-        <v>56.32</v>
+        <v>133.6</v>
       </c>
       <c r="D453" t="n">
-        <v>22404</v>
+        <v>15545</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>101.82</v>
+        <v>163.81</v>
       </c>
       <c r="B454" t="n">
-        <v>46424</v>
+        <v>28509</v>
       </c>
       <c r="C454" t="n">
-        <v>102.82</v>
+        <v>163.24</v>
       </c>
       <c r="D454" t="n">
-        <v>12278</v>
+        <v>24073</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>92.01000000000001</v>
+        <v>164.04</v>
       </c>
       <c r="B455" t="n">
-        <v>24843</v>
+        <v>29150</v>
       </c>
       <c r="C455" t="n">
-        <v>89.2</v>
+        <v>154.84</v>
       </c>
       <c r="D455" t="n">
-        <v>23988</v>
+        <v>28048</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>111.48</v>
+        <v>164.04</v>
       </c>
       <c r="B456" t="n">
-        <v>26737</v>
+        <v>27521</v>
       </c>
       <c r="C456" t="n">
-        <v>110.02</v>
+        <v>180</v>
       </c>
       <c r="D456" t="n">
-        <v>17591</v>
+        <v>17215</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>96.79000000000001</v>
+        <v>164.06</v>
       </c>
       <c r="B457" t="n">
-        <v>35400</v>
+        <v>26423</v>
       </c>
       <c r="C457" t="n">
-        <v>97.25</v>
+        <v>175.48</v>
       </c>
       <c r="D457" t="n">
-        <v>16393</v>
+        <v>21418</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>168.93</v>
+        <v>164.79</v>
       </c>
       <c r="B458" t="n">
-        <v>22977</v>
+        <v>28606</v>
       </c>
       <c r="C458" t="n">
-        <v>171.62</v>
+        <v>143.61</v>
       </c>
       <c r="D458" t="n">
-        <v>14681</v>
+        <v>11559</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>102.43</v>
+        <v>165.6</v>
       </c>
       <c r="B459" t="n">
-        <v>45104</v>
+        <v>26186</v>
       </c>
       <c r="C459" t="n">
-        <v>104.4</v>
+        <v>132.26</v>
       </c>
       <c r="D459" t="n">
-        <v>14081</v>
+        <v>24585</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>113.85</v>
+        <v>165.74</v>
       </c>
       <c r="B460" t="n">
-        <v>22446</v>
+        <v>28528</v>
       </c>
       <c r="C460" t="n">
-        <v>113.18</v>
+        <v>144.3</v>
       </c>
       <c r="D460" t="n">
-        <v>10015</v>
+        <v>20552</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>94.34</v>
+        <v>166.51</v>
       </c>
       <c r="B461" t="n">
-        <v>30383</v>
+        <v>25408</v>
       </c>
       <c r="C461" t="n">
-        <v>90.84</v>
+        <v>172.29</v>
       </c>
       <c r="D461" t="n">
-        <v>12958</v>
+        <v>19309</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>114.72</v>
+        <v>168.37</v>
       </c>
       <c r="B462" t="n">
-        <v>23954</v>
+        <v>26651</v>
       </c>
       <c r="C462" t="n">
-        <v>114.58</v>
+        <v>172.31</v>
       </c>
       <c r="D462" t="n">
-        <v>20220</v>
+        <v>27572</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>98.91</v>
+        <v>168.44</v>
       </c>
       <c r="B463" t="n">
-        <v>44693</v>
+        <v>23995</v>
       </c>
       <c r="C463" t="n">
-        <v>98.64</v>
+        <v>164.78</v>
       </c>
       <c r="D463" t="n">
-        <v>13700</v>
+        <v>24398</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>131.3</v>
+        <v>168.53</v>
       </c>
       <c r="B464" t="n">
-        <v>22443</v>
+        <v>25152</v>
       </c>
       <c r="C464" t="n">
-        <v>132.7</v>
+        <v>180</v>
       </c>
       <c r="D464" t="n">
-        <v>21730</v>
+        <v>10205</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>101.66</v>
+        <v>168.7</v>
       </c>
       <c r="B465" t="n">
-        <v>45942</v>
+        <v>22651</v>
       </c>
       <c r="C465" t="n">
-        <v>104.95</v>
+        <v>180</v>
       </c>
       <c r="D465" t="n">
-        <v>20472</v>
+        <v>28624</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>40.45</v>
+        <v>168.85</v>
       </c>
       <c r="B466" t="n">
-        <v>26217</v>
+        <v>23292</v>
       </c>
       <c r="C466" t="n">
-        <v>38.91</v>
+        <v>144.38</v>
       </c>
       <c r="D466" t="n">
-        <v>20647</v>
+        <v>21835</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>114.12</v>
+        <v>169.34</v>
       </c>
       <c r="B467" t="n">
-        <v>24766</v>
+        <v>24710</v>
       </c>
       <c r="C467" t="n">
-        <v>115.06</v>
+        <v>159.42</v>
       </c>
       <c r="D467" t="n">
-        <v>19208</v>
+        <v>16757</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>94.79000000000001</v>
+        <v>169.51</v>
       </c>
       <c r="B468" t="n">
-        <v>33217</v>
+        <v>24107</v>
       </c>
       <c r="C468" t="n">
-        <v>97.73</v>
+        <v>168.75</v>
       </c>
       <c r="D468" t="n">
-        <v>25169</v>
+        <v>16257</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>127.56</v>
+        <v>169.53</v>
       </c>
       <c r="B469" t="n">
-        <v>21533</v>
+        <v>24621</v>
       </c>
       <c r="C469" t="n">
-        <v>122.87</v>
+        <v>180</v>
       </c>
       <c r="D469" t="n">
-        <v>21106</v>
+        <v>23642</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>103.89</v>
+        <v>170.05</v>
       </c>
       <c r="B470" t="n">
-        <v>45602</v>
+        <v>22254</v>
       </c>
       <c r="C470" t="n">
-        <v>103.02</v>
+        <v>180</v>
       </c>
       <c r="D470" t="n">
-        <v>23488</v>
+        <v>13684</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>98.56999999999999</v>
+        <v>170.11</v>
       </c>
       <c r="B471" t="n">
-        <v>39851</v>
+        <v>25968</v>
       </c>
       <c r="C471" t="n">
-        <v>101.81</v>
+        <v>180</v>
       </c>
       <c r="D471" t="n">
-        <v>25912</v>
+        <v>27936</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>114.59</v>
+        <v>170.2</v>
       </c>
       <c r="B472" t="n">
-        <v>22602</v>
+        <v>23635</v>
       </c>
       <c r="C472" t="n">
-        <v>110.17</v>
+        <v>146.76</v>
       </c>
       <c r="D472" t="n">
-        <v>29580</v>
+        <v>17918</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>110.82</v>
+        <v>170.38</v>
       </c>
       <c r="B473" t="n">
-        <v>31205</v>
+        <v>25621</v>
       </c>
       <c r="C473" t="n">
-        <v>113.38</v>
+        <v>164.99</v>
       </c>
       <c r="D473" t="n">
-        <v>18859</v>
+        <v>18043</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>3.61</v>
+        <v>170.39</v>
       </c>
       <c r="B474" t="n">
-        <v>24260</v>
+        <v>22951</v>
       </c>
       <c r="C474" t="n">
-        <v>3.82</v>
+        <v>157.5</v>
       </c>
       <c r="D474" t="n">
-        <v>20640</v>
+        <v>28184</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>90.54000000000001</v>
+        <v>170.51</v>
       </c>
       <c r="B475" t="n">
-        <v>24859</v>
+        <v>21257</v>
       </c>
       <c r="C475" t="n">
-        <v>89.88</v>
+        <v>171.27</v>
       </c>
       <c r="D475" t="n">
-        <v>26705</v>
+        <v>28548</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>100.6</v>
+        <v>170.77</v>
       </c>
       <c r="B476" t="n">
-        <v>45941</v>
+        <v>21732</v>
       </c>
       <c r="C476" t="n">
-        <v>101.8</v>
+        <v>180</v>
       </c>
       <c r="D476" t="n">
-        <v>13049</v>
+        <v>12781</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>100.92</v>
+        <v>170.86</v>
       </c>
       <c r="B477" t="n">
-        <v>44683</v>
+        <v>20545</v>
       </c>
       <c r="C477" t="n">
-        <v>102.87</v>
+        <v>180</v>
       </c>
       <c r="D477" t="n">
-        <v>12942</v>
+        <v>10083</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>95.64</v>
+        <v>170.87</v>
       </c>
       <c r="B478" t="n">
-        <v>34807</v>
+        <v>20768</v>
       </c>
       <c r="C478" t="n">
-        <v>98.52</v>
+        <v>157.31</v>
       </c>
       <c r="D478" t="n">
-        <v>20852</v>
+        <v>29301</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>100.2</v>
+        <v>171.14</v>
       </c>
       <c r="B479" t="n">
-        <v>42173</v>
+        <v>23824</v>
       </c>
       <c r="C479" t="n">
-        <v>102.3</v>
+        <v>156</v>
       </c>
       <c r="D479" t="n">
-        <v>27616</v>
+        <v>24734</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>90.01000000000001</v>
+        <v>172.28</v>
       </c>
       <c r="B480" t="n">
-        <v>23886</v>
+        <v>22759</v>
       </c>
       <c r="C480" t="n">
-        <v>92.34</v>
+        <v>180</v>
       </c>
       <c r="D480" t="n">
-        <v>21989</v>
+        <v>18234</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>114.1</v>
+        <v>172.69</v>
       </c>
       <c r="B481" t="n">
-        <v>24497</v>
+        <v>20394</v>
       </c>
       <c r="C481" t="n">
-        <v>109.85</v>
+        <v>165.52</v>
       </c>
       <c r="D481" t="n">
-        <v>15167</v>
+        <v>24463</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>108</v>
+        <v>173.03</v>
       </c>
       <c r="B482" t="n">
-        <v>35974</v>
+        <v>21002</v>
       </c>
       <c r="C482" t="n">
-        <v>110.37</v>
+        <v>142.68</v>
       </c>
       <c r="D482" t="n">
-        <v>12672</v>
+        <v>20444</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>97.27</v>
+        <v>173.09</v>
       </c>
       <c r="B483" t="n">
-        <v>39935</v>
+        <v>20022</v>
       </c>
       <c r="C483" t="n">
-        <v>100.5</v>
+        <v>180</v>
       </c>
       <c r="D483" t="n">
-        <v>25801</v>
+        <v>11053</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>96.92</v>
+        <v>174.27</v>
       </c>
       <c r="B484" t="n">
-        <v>39455</v>
+        <v>19676</v>
       </c>
       <c r="C484" t="n">
-        <v>98.78</v>
+        <v>162.05</v>
       </c>
       <c r="D484" t="n">
-        <v>12570</v>
+        <v>26377</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>139.15</v>
+        <v>174.46</v>
       </c>
       <c r="B485" t="n">
-        <v>24178</v>
+        <v>19512</v>
       </c>
       <c r="C485" t="n">
-        <v>133.98</v>
+        <v>180</v>
       </c>
       <c r="D485" t="n">
-        <v>17049</v>
+        <v>14901</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>3.5</v>
+        <v>174.79</v>
       </c>
       <c r="B486" t="n">
-        <v>24962</v>
+        <v>19442</v>
       </c>
       <c r="C486" t="n">
-        <v>4.24</v>
+        <v>180</v>
       </c>
       <c r="D486" t="n">
-        <v>19398</v>
+        <v>28113</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>108.87</v>
+        <v>175.07</v>
       </c>
       <c r="B487" t="n">
-        <v>33896</v>
+        <v>19415</v>
       </c>
       <c r="C487" t="n">
-        <v>112.17</v>
+        <v>180</v>
       </c>
       <c r="D487" t="n">
-        <v>16243</v>
+        <v>27903</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>94.84999999999999</v>
+        <v>175.25</v>
       </c>
       <c r="B488" t="n">
-        <v>33515</v>
+        <v>17305</v>
       </c>
       <c r="C488" t="n">
-        <v>92.87</v>
+        <v>180</v>
       </c>
       <c r="D488" t="n">
-        <v>10891</v>
+        <v>29287</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>114.36</v>
+        <v>175.41</v>
       </c>
       <c r="B489" t="n">
-        <v>22778</v>
+        <v>20003</v>
       </c>
       <c r="C489" t="n">
-        <v>113.16</v>
+        <v>144.41</v>
       </c>
       <c r="D489" t="n">
-        <v>10696</v>
+        <v>15414</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>103.47</v>
+        <v>176.36</v>
       </c>
       <c r="B490" t="n">
-        <v>47571</v>
+        <v>18623</v>
       </c>
       <c r="C490" t="n">
-        <v>103.81</v>
+        <v>180</v>
       </c>
       <c r="D490" t="n">
-        <v>17819</v>
+        <v>29467</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>100.74</v>
+        <v>177.17</v>
       </c>
       <c r="B491" t="n">
-        <v>41881</v>
+        <v>18483</v>
       </c>
       <c r="C491" t="n">
-        <v>100.54</v>
+        <v>180</v>
       </c>
       <c r="D491" t="n">
-        <v>11810</v>
+        <v>10079</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>97.68000000000001</v>
+        <v>177.43</v>
       </c>
       <c r="B492" t="n">
-        <v>41352</v>
+        <v>16905</v>
       </c>
       <c r="C492" t="n">
-        <v>102.82</v>
+        <v>180</v>
       </c>
       <c r="D492" t="n">
-        <v>25325</v>
+        <v>24249</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>98.62</v>
+        <v>177.49</v>
       </c>
       <c r="B493" t="n">
-        <v>43507</v>
+        <v>18774</v>
       </c>
       <c r="C493" t="n">
-        <v>100.49</v>
+        <v>146.59</v>
       </c>
       <c r="D493" t="n">
-        <v>24771</v>
+        <v>21388</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>92.52</v>
+        <v>177.93</v>
       </c>
       <c r="B494" t="n">
-        <v>26652</v>
+        <v>17883</v>
       </c>
       <c r="C494" t="n">
-        <v>95.7</v>
+        <v>180</v>
       </c>
       <c r="D494" t="n">
-        <v>16716</v>
+        <v>26877</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>94.90000000000001</v>
+        <v>178.16</v>
       </c>
       <c r="B495" t="n">
-        <v>33150</v>
+        <v>21105</v>
       </c>
       <c r="C495" t="n">
-        <v>98.41</v>
+        <v>144.58</v>
       </c>
       <c r="D495" t="n">
-        <v>17246</v>
+        <v>20967</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>108.62</v>
+        <v>178.43</v>
       </c>
       <c r="B496" t="n">
-        <v>37315</v>
+        <v>19042</v>
       </c>
       <c r="C496" t="n">
-        <v>112.01</v>
+        <v>180</v>
       </c>
       <c r="D496" t="n">
-        <v>18233</v>
+        <v>29740</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>102.48</v>
+        <v>178.67</v>
       </c>
       <c r="B497" t="n">
-        <v>47654</v>
+        <v>21131</v>
       </c>
       <c r="C497" t="n">
-        <v>106.91</v>
+        <v>161.14</v>
       </c>
       <c r="D497" t="n">
-        <v>26635</v>
+        <v>27611</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>114.53</v>
+        <v>178.99</v>
       </c>
       <c r="B498" t="n">
-        <v>21950</v>
+        <v>19495</v>
       </c>
       <c r="C498" t="n">
-        <v>117.38</v>
+        <v>180</v>
       </c>
       <c r="D498" t="n">
-        <v>20935</v>
+        <v>19561</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>106.22</v>
+        <v>179.43</v>
       </c>
       <c r="B499" t="n">
-        <v>41297</v>
+        <v>19561</v>
       </c>
       <c r="C499" t="n">
-        <v>103.46</v>
+        <v>180</v>
       </c>
       <c r="D499" t="n">
-        <v>18137</v>
+        <v>17768</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>92.42</v>
+        <v>179.44</v>
       </c>
       <c r="B500" t="n">
-        <v>26483</v>
+        <v>18561</v>
       </c>
       <c r="C500" t="n">
-        <v>88.67</v>
+        <v>180</v>
       </c>
       <c r="D500" t="n">
-        <v>23008</v>
+        <v>24921</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>103.89</v>
+        <v>180</v>
       </c>
       <c r="B501" t="n">
-        <v>49224</v>
+        <v>18204</v>
       </c>
       <c r="C501" t="n">
-        <v>107.43</v>
+        <v>161.64</v>
       </c>
       <c r="D501" t="n">
-        <v>18322</v>
+        <v>10505</v>
       </c>
     </row>
   </sheetData>
